--- a/employees.xlsx
+++ b/employees.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الموظفين" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تعليمات" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="العقود" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإجازات" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الهويات" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تعليمات" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,19 +476,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -507,37 +504,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>رقم الهوية / الإقامة</t>
+          <t>تاريخ بداية العقد</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>تاريخ انتهاء الهوية / الإقامة</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ بداية العقد</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>تاريخ انتهاء العقد</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>حالة الموظف</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ بداية الإجازة</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ نهاية الإجازة</t>
         </is>
       </c>
     </row>
@@ -557,27 +529,12 @@
           <t>المبيعات</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>1012345678</t>
-        </is>
+      <c r="D2" s="4" t="n">
+        <v>45937</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>45937</v>
-      </c>
-      <c r="G2" s="4" t="n">
         <v>46257</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>على رأس العمل</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -595,30 +552,11 @@
           <t>الموارد البشرية</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2098765432</t>
-        </is>
+      <c r="D3" s="4" t="n">
+        <v>45637</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>46437</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>45637</v>
-      </c>
-      <c r="G3" s="4" t="n">
         <v>46637</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>في إجازة</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>46235</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>46245</v>
       </c>
     </row>
     <row r="4">
@@ -637,27 +575,12 @@
           <t>تقنية المعلومات</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1055512345</t>
-        </is>
+      <c r="D4" s="4" t="n">
+        <v>46137</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>46247</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>46137</v>
-      </c>
-      <c r="G4" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>على رأس العمل</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -675,27 +598,12 @@
           <t>المالية</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2044455566</t>
-        </is>
+      <c r="D5" s="4" t="n">
+        <v>45337</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>46737</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>45337</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>46737</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>على رأس العمل</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -708,7 +616,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>الاسم</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>الرقم الوظيفي</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ بداية الإجازة</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ نهاية الإجازة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>نورة محمد القحطاني</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>EMP-1002</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>46245</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>الاسم</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>الرقم الوظيفي</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الهوية / الإقامة</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ انتهاء الهوية / الإقامة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>أحمد سالم العتيبي</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>EMP-1001</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>1012345678</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>نورة محمد القحطاني</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>EMP-1002</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2098765432</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>46437</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>خالد إبراهيم الدوسري</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EMP-1003</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1055512345</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>سارة عبدالله الشهري</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>EMP-1004</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2044455566</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>46737</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -734,7 +835,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>الشيت المهم هو شيت (الموظفين) — أضف صفًا لكل موظف بنفس ترتيب الأعمدة.</t>
+          <t>الملف مقسّم إلى 3 شيتات منفصلة، كل شيت مستقل تمامًا عن الآخر — عدّل أي واحد لوحده دون التأثير على الباقي:</t>
         </is>
       </c>
     </row>
@@ -744,73 +845,100 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>شرح الأعمدة:</t>
+          <t>1) شيت "العقود": بيانات عقود الموظفين.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>• الاسم / الرقم الوظيفي / القسم: بيانات تعريفية عامة.</t>
+          <t xml:space="preserve">   الأعمدة: الاسم، الرقم الوظيفي، القسم، تاريخ بداية العقد، تاريخ انتهاء العقد.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>• رقم الهوية / الإقامة: رقم الهوية الوطنية أو الإقامة.</t>
-        </is>
-      </c>
+      <c r="A8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>• تاريخ انتهاء الهوية / الإقامة: تُستخدم لحساب عدد الأيام المتبقية وتنبيه "تنتهي قريبًا".</t>
+          <t>2) شيت "الإجازات": أضف صفًا فقط للموظف الذي لديه إجازة (حالية أو قادمة).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>• تاريخ بداية العقد وتاريخ انتهاء العقد: تُستخدم لحساب الأيام المتبقية على انتهاء العقد.</t>
+          <t xml:space="preserve">   الأعمدة: الاسم، الرقم الوظيفي، القسم، تاريخ بداية الإجازة، تاريخ نهاية الإجازة.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>• حالة الموظف: اكتب "في إجازة" أو "على رأس العمل" (بالضبط بهذا الشكل حتى تُحتسب صح).</t>
+          <t xml:space="preserve">   الصفحة تحسب تلقائيًا هل الإجازة سارية اليوم بمقارنة التاريخين — لا حاجة لكتابة "في إجازة" يدويًا.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>• تاريخ بداية الإجازة وتاريخ نهاية الإجازة: تُعبّى فقط إذا كانت الحالة "في إجازة".</t>
-        </is>
-      </c>
+      <c r="A12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr"/>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>3) شيت "الهويات": بيانات الهوية الوطنية / الإقامة.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>بعد أي تعديل: احفظ الملف، ثم ارفعه (Commit) على نفس المسار في مستودع GitHub</t>
+          <t xml:space="preserve">   الأعمدة: الاسم، الرقم الوظيفي، رقم الهوية / الإقامة، تاريخ انتهاء الهوية / الإقامة.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>باسم الملف نفسه (employees.xlsx) — الصفحة تقرأ الملف مباشرة من المستودع في كل فتح.</t>
-        </is>
-      </c>
+      <c r="A15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>لا حاجة لتعديل أي كود.</t>
+          <t>ملاحظات عامة:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>• التواريخ يجب أن تكون تاريخ حقيقي (Date) من إكسل، وليست نصًا مكتوبًا.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>• لا حاجة لتكرار كل بيانات الموظف بكل شيت — فقط الأعمدة المطلوبة بذلك الشيت.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>• بعد أي تعديل: احفظ الملف، ثم ارفعه (Commit) على نفس المسار في مستودع GitHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  باسم الملف نفسه (employees.xlsx) — الصفحة تقرأ الملف مباشرة من المستودع في كل فتح.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>• لا حاجة لتعديل أي كود إطلاقًا.</t>
         </is>
       </c>
     </row>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moham\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/hail work/HAIL-HOUSE-Hr-Me/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3556AC-ED05-4CC8-88D4-79A17DABA4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_5B98D5C5A47B8C952F9A91E094CC3D22B97D2674" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77EB162D-8DA1-414D-8E8F-9C0C950DB0EF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="العقود" sheetId="1" r:id="rId1"/>
@@ -19,19 +19,8 @@
     <sheet name="تعليمات" sheetId="4" r:id="rId4"/>
     <sheet name="بيانات الموظفين" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -40,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="247">
   <si>
     <t>الاسم</t>
   </si>
@@ -660,6 +649,9 @@
     <t>تاريخ نهاية الإجازة</t>
   </si>
   <si>
+    <t>نوع الإجازة</t>
+  </si>
+  <si>
     <t>رقم الهوية / الإقامة</t>
   </si>
   <si>
@@ -741,6 +733,18 @@
     <t>اسم الشيت يجب أن يبقى "بيانات الموظفين" بالضبط حتى تقرأه الصفحة تلقائيًا.</t>
   </si>
   <si>
+    <t>عمود جديد بشيت "الإجازات": "نوع الإجازة"</t>
+  </si>
+  <si>
+    <t>اكتب نوع كل إجازة (مثال: إجازة سنوية، إجازة مرضية، إجازة زواج، رحلة عمل، إجازة بدون راتب...).</t>
+  </si>
+  <si>
+    <t>الصفحة تعطي كل نوع لونًا ثابتًا تلقائيًا في الجداول والتقويم — لا حاجة لتحديد الألوان يدويًا.</t>
+  </si>
+  <si>
+    <t>الخلايا الفاضية تظهر بالصفحة كـ "غير محدد" بلون رمادي، فلا تسبب أي خطأ.</t>
+  </si>
+  <si>
     <t>الفرع</t>
   </si>
   <si>
@@ -756,115 +760,16 @@
     <t>تاريخ الميلاد</t>
   </si>
   <si>
-    <t>الإدارة الرئيسية</t>
-  </si>
-  <si>
-    <t>اردني</t>
-  </si>
-  <si>
-    <t>سعودي</t>
-  </si>
-  <si>
-    <t>سوري</t>
-  </si>
-  <si>
-    <t>الزلفي</t>
-  </si>
-  <si>
-    <t>سوداني</t>
-  </si>
-  <si>
-    <t>نيبالي</t>
-  </si>
-  <si>
-    <t>صالة الرياض</t>
-  </si>
-  <si>
-    <t>هندي</t>
-  </si>
-  <si>
-    <t>مصنع ومستودع الرياض</t>
-  </si>
-  <si>
-    <t>باكستاني</t>
-  </si>
-  <si>
-    <t>بيت هائل للنقليات</t>
-  </si>
-  <si>
-    <t>لبناني</t>
-  </si>
-  <si>
-    <t>مصري</t>
-  </si>
-  <si>
-    <t>مينمار</t>
-  </si>
-  <si>
-    <t>القبائل المهاجرة</t>
-  </si>
-  <si>
-    <t>بنجلاديشى</t>
-  </si>
-  <si>
-    <t>فليبيني</t>
-  </si>
-  <si>
-    <t>يمني</t>
-  </si>
-  <si>
-    <t>عامر بوشي</t>
-  </si>
-  <si>
-    <t>ياسر بوشي</t>
-  </si>
-  <si>
-    <t>انس بوشي</t>
-  </si>
-  <si>
-    <t>امجد حلح</t>
-  </si>
-  <si>
-    <t>زياد المبيض</t>
-  </si>
-  <si>
-    <t>حمدان الحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابوزيد</t>
-  </si>
-  <si>
-    <t>حسام السبسبي</t>
-  </si>
-  <si>
-    <t>رشيد الحمد</t>
-  </si>
-  <si>
-    <t>احمد الخطيب</t>
-  </si>
-  <si>
-    <t>محمد الباتل</t>
-  </si>
-  <si>
-    <t>عبيده الحايك</t>
-  </si>
-  <si>
-    <t>خالد الجيجاوي</t>
-  </si>
-  <si>
-    <t>سليمان المطير</t>
-  </si>
-  <si>
-    <t>احمد قطب</t>
-  </si>
-  <si>
-    <t>محمود حدق</t>
-  </si>
-  <si>
-    <t>شكيب الكسواني</t>
-  </si>
-  <si>
-    <t>مجد حمدو</t>
+    <t>استثنائية</t>
+  </si>
+  <si>
+    <t>إجازة اختبارات</t>
+  </si>
+  <si>
+    <t>إجازة سنوية</t>
+  </si>
+  <si>
+    <t>اجازة بدون راتب</t>
   </si>
 </sst>
 </file>
@@ -874,7 +779,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -887,22 +792,26 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF1F3B57"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -985,7 +894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1011,9 +920,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1319,7 +1225,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H181"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
@@ -1328,7 +1234,7 @@
     <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32.1" customHeight="1">
+    <row r="1" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1345,7 +1251,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
@@ -1363,7 +1269,7 @@
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -1381,7 +1287,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
@@ -1399,7 +1305,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1417,7 +1323,7 @@
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>13</v>
       </c>
@@ -1435,7 +1341,7 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>15</v>
       </c>
@@ -1453,7 +1359,7 @@
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>17</v>
       </c>
@@ -1471,7 +1377,7 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>18</v>
       </c>
@@ -1489,7 +1395,7 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
@@ -1507,7 +1413,7 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>21</v>
       </c>
@@ -1525,7 +1431,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
@@ -1543,7 +1449,7 @@
       </c>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -1561,7 +1467,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>26</v>
       </c>
@@ -1579,7 +1485,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>27</v>
       </c>
@@ -1597,7 +1503,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>28</v>
       </c>
@@ -1615,7 +1521,7 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
@@ -1632,7 +1538,7 @@
         <v>46440</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>31</v>
       </c>
@@ -1649,7 +1555,7 @@
         <v>46393</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -1666,7 +1572,7 @@
         <v>46823</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>33</v>
       </c>
@@ -1683,7 +1589,7 @@
         <v>46414</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>34</v>
       </c>
@@ -1700,7 +1606,7 @@
         <v>46410</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>35</v>
       </c>
@@ -1717,7 +1623,7 @@
         <v>46356</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>36</v>
       </c>
@@ -1734,7 +1640,7 @@
         <v>46569</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>38</v>
       </c>
@@ -1751,7 +1657,7 @@
         <v>46447</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>39</v>
       </c>
@@ -1768,7 +1674,7 @@
         <v>46411</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>41</v>
       </c>
@@ -1785,7 +1691,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>42</v>
       </c>
@@ -1802,7 +1708,7 @@
         <v>46341</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>44</v>
       </c>
@@ -1819,7 +1725,7 @@
         <v>46299</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>45</v>
       </c>
@@ -1836,7 +1742,7 @@
         <v>46242</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>46</v>
       </c>
@@ -1853,7 +1759,7 @@
         <v>46367</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>47</v>
       </c>
@@ -1870,7 +1776,7 @@
         <v>46568</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>48</v>
       </c>
@@ -1887,7 +1793,7 @@
         <v>46350</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>49</v>
       </c>
@@ -1904,7 +1810,7 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>50</v>
       </c>
@@ -1921,7 +1827,7 @@
         <v>46486</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>51</v>
       </c>
@@ -1938,7 +1844,7 @@
         <v>46477</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>52</v>
       </c>
@@ -1955,7 +1861,7 @@
         <v>46388</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>53</v>
       </c>
@@ -1972,7 +1878,7 @@
         <v>46388</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>54</v>
       </c>
@@ -1989,7 +1895,7 @@
         <v>46559</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>55</v>
       </c>
@@ -2006,7 +1912,7 @@
         <v>46345</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>56</v>
       </c>
@@ -2023,7 +1929,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>57</v>
       </c>
@@ -2040,7 +1946,7 @@
         <v>46541</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>58</v>
       </c>
@@ -2057,7 +1963,7 @@
         <v>46519</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>59</v>
       </c>
@@ -2074,7 +1980,7 @@
         <v>46376</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>60</v>
       </c>
@@ -2091,7 +1997,7 @@
         <v>46401</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>61</v>
       </c>
@@ -2108,7 +2014,7 @@
         <v>46405</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>63</v>
       </c>
@@ -2125,7 +2031,7 @@
         <v>46427</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>64</v>
       </c>
@@ -2142,7 +2048,7 @@
         <v>46447</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>65</v>
       </c>
@@ -2159,7 +2065,7 @@
         <v>46635</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>66</v>
       </c>
@@ -2176,7 +2082,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>67</v>
       </c>
@@ -2193,7 +2099,7 @@
         <v>47065</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>68</v>
       </c>
@@ -2210,7 +2116,7 @@
         <v>46296</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>69</v>
       </c>
@@ -2227,7 +2133,7 @@
         <v>46316</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>70</v>
       </c>
@@ -2244,7 +2150,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>72</v>
       </c>
@@ -2261,7 +2167,7 @@
         <v>46341</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>73</v>
       </c>
@@ -2278,7 +2184,7 @@
         <v>46406</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>74</v>
       </c>
@@ -2295,7 +2201,7 @@
         <v>46819</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>75</v>
       </c>
@@ -2312,7 +2218,7 @@
         <v>46425</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>77</v>
       </c>
@@ -2329,7 +2235,7 @@
         <v>46446</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>78</v>
       </c>
@@ -2346,7 +2252,7 @@
         <v>46452</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>79</v>
       </c>
@@ -2363,7 +2269,7 @@
         <v>46900</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>80</v>
       </c>
@@ -2380,7 +2286,7 @@
         <v>46926</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>81</v>
       </c>
@@ -2397,7 +2303,7 @@
         <v>46954</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>82</v>
       </c>
@@ -2414,7 +2320,7 @@
         <v>46977</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>83</v>
       </c>
@@ -2431,7 +2337,7 @@
         <v>46977</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>84</v>
       </c>
@@ -2448,7 +2354,7 @@
         <v>46569</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>85</v>
       </c>
@@ -2465,7 +2371,7 @@
         <v>46605</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>86</v>
       </c>
@@ -2482,7 +2388,7 @@
         <v>46610</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>87</v>
       </c>
@@ -2499,7 +2405,7 @@
         <v>46610</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>88</v>
       </c>
@@ -2516,7 +2422,7 @@
         <v>47061</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>89</v>
       </c>
@@ -2533,7 +2439,7 @@
         <v>47061</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>90</v>
       </c>
@@ -2550,7 +2456,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>91</v>
       </c>
@@ -2567,7 +2473,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>92</v>
       </c>
@@ -2584,7 +2490,7 @@
         <v>46304</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>94</v>
       </c>
@@ -2601,7 +2507,7 @@
         <v>46310</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>96</v>
       </c>
@@ -2618,7 +2524,7 @@
         <v>46323</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>97</v>
       </c>
@@ -2635,7 +2541,7 @@
         <v>46324</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>98</v>
       </c>
@@ -2652,7 +2558,7 @@
         <v>46325</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>99</v>
       </c>
@@ -2669,7 +2575,7 @@
         <v>46341</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>100</v>
       </c>
@@ -2686,7 +2592,7 @@
         <v>46320</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>101</v>
       </c>
@@ -2703,7 +2609,7 @@
         <v>46355</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>102</v>
       </c>
@@ -2720,7 +2626,7 @@
         <v>46358</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>103</v>
       </c>
@@ -2737,7 +2643,7 @@
         <v>46374</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>104</v>
       </c>
@@ -2754,7 +2660,7 @@
         <v>46377</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>105</v>
       </c>
@@ -2771,7 +2677,7 @@
         <v>46384</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>106</v>
       </c>
@@ -2788,7 +2694,7 @@
         <v>46390</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
         <v>107</v>
       </c>
@@ -2805,7 +2711,7 @@
         <v>46480</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>108</v>
       </c>
@@ -2822,7 +2728,7 @@
         <v>46421</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>109</v>
       </c>
@@ -2839,7 +2745,7 @@
         <v>46436</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>110</v>
       </c>
@@ -2856,7 +2762,7 @@
         <v>46441</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>111</v>
       </c>
@@ -2873,7 +2779,7 @@
         <v>46472</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>112</v>
       </c>
@@ -2890,7 +2796,7 @@
         <v>46525</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>113</v>
       </c>
@@ -2907,7 +2813,7 @@
         <v>46525</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>114</v>
       </c>
@@ -2924,7 +2830,7 @@
         <v>46558</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>115</v>
       </c>
@@ -2941,7 +2847,7 @@
         <v>46558</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>116</v>
       </c>
@@ -2958,7 +2864,7 @@
         <v>46558</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
         <v>117</v>
       </c>
@@ -2975,7 +2881,7 @@
         <v>46558</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>118</v>
       </c>
@@ -2992,7 +2898,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
         <v>119</v>
       </c>
@@ -3009,7 +2915,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>120</v>
       </c>
@@ -3026,7 +2932,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
         <v>121</v>
       </c>
@@ -3043,7 +2949,7 @@
         <v>46587</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
         <v>122</v>
       </c>
@@ -3060,7 +2966,7 @@
         <v>46657</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
         <v>123</v>
       </c>
@@ -3077,7 +2983,7 @@
         <v>46404</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>124</v>
       </c>
@@ -3094,7 +3000,7 @@
         <v>46775</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
         <v>125</v>
       </c>
@@ -3111,7 +3017,7 @@
         <v>46775</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>126</v>
       </c>
@@ -3128,7 +3034,7 @@
         <v>46775</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>127</v>
       </c>
@@ -3145,7 +3051,7 @@
         <v>46775</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>128</v>
       </c>
@@ -3162,7 +3068,7 @@
         <v>46843</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>129</v>
       </c>
@@ -3179,7 +3085,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>131</v>
       </c>
@@ -3196,7 +3102,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>132</v>
       </c>
@@ -3213,7 +3119,7 @@
         <v>46476</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>133</v>
       </c>
@@ -3230,7 +3136,7 @@
         <v>47019</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
         <v>134</v>
       </c>
@@ -3247,7 +3153,7 @@
         <v>46839</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
         <v>135</v>
       </c>
@@ -3264,7 +3170,7 @@
         <v>46439</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>136</v>
       </c>
@@ -3281,7 +3187,7 @@
         <v>46928</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>137</v>
       </c>
@@ -3298,7 +3204,7 @@
         <v>46599</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
         <v>138</v>
       </c>
@@ -3315,7 +3221,7 @@
         <v>46453</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>139</v>
       </c>
@@ -3332,7 +3238,7 @@
         <v>46363</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
         <v>140</v>
       </c>
@@ -3349,7 +3255,7 @@
         <v>46405</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>141</v>
       </c>
@@ -3366,7 +3272,7 @@
         <v>46477</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
         <v>142</v>
       </c>
@@ -3383,7 +3289,7 @@
         <v>46671</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
         <v>143</v>
       </c>
@@ -3400,7 +3306,7 @@
         <v>46671</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>144</v>
       </c>
@@ -3417,7 +3323,7 @@
         <v>46671</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
         <v>145</v>
       </c>
@@ -3434,7 +3340,7 @@
         <v>46671</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
         <v>146</v>
       </c>
@@ -3451,7 +3357,7 @@
         <v>46492</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>147</v>
       </c>
@@ -3468,7 +3374,7 @@
         <v>46867</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
         <v>148</v>
       </c>
@@ -3485,7 +3391,7 @@
         <v>46867</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>149</v>
       </c>
@@ -3502,7 +3408,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
         <v>150</v>
       </c>
@@ -3519,7 +3425,7 @@
         <v>46382</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
         <v>151</v>
       </c>
@@ -3536,7 +3442,7 @@
         <v>46568</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>152</v>
       </c>
@@ -3553,7 +3459,7 @@
         <v>46390</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
         <v>153</v>
       </c>
@@ -3570,7 +3476,7 @@
         <v>46574</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
         <v>154</v>
       </c>
@@ -3587,7 +3493,7 @@
         <v>46590</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
         <v>155</v>
       </c>
@@ -3604,7 +3510,7 @@
         <v>46599</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
         <v>156</v>
       </c>
@@ -3621,7 +3527,7 @@
         <v>46599</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
         <v>157</v>
       </c>
@@ -3638,7 +3544,7 @@
         <v>46442</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
         <v>158</v>
       </c>
@@ -3655,7 +3561,7 @@
         <v>46630</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>159</v>
       </c>
@@ -3672,7 +3578,7 @@
         <v>46522</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
         <v>160</v>
       </c>
@@ -3689,7 +3595,7 @@
         <v>46400</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
         <v>161</v>
       </c>
@@ -3706,7 +3612,7 @@
         <v>46560</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
         <v>162</v>
       </c>
@@ -3723,7 +3629,7 @@
         <v>46561</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
         <v>163</v>
       </c>
@@ -3740,7 +3646,7 @@
         <v>46560</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
         <v>164</v>
       </c>
@@ -3757,7 +3663,7 @@
         <v>46912</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
         <v>165</v>
       </c>
@@ -3774,7 +3680,7 @@
         <v>46912</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
         <v>166</v>
       </c>
@@ -3791,7 +3697,7 @@
         <v>46573</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
         <v>167</v>
       </c>
@@ -3808,7 +3714,7 @@
         <v>47029</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
         <v>168</v>
       </c>
@@ -3825,7 +3731,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
         <v>169</v>
       </c>
@@ -3842,7 +3748,7 @@
         <v>46442</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>170</v>
       </c>
@@ -3859,7 +3765,7 @@
         <v>46355</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
         <v>171</v>
       </c>
@@ -3876,7 +3782,7 @@
         <v>46457</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
         <v>172</v>
       </c>
@@ -3893,7 +3799,7 @@
         <v>46495</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>173</v>
       </c>
@@ -3910,7 +3816,7 @@
         <v>46496</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>174</v>
       </c>
@@ -3927,7 +3833,7 @@
         <v>46496</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
         <v>175</v>
       </c>
@@ -3944,7 +3850,7 @@
         <v>46410</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>176</v>
       </c>
@@ -3961,7 +3867,7 @@
         <v>46948</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>177</v>
       </c>
@@ -3978,7 +3884,7 @@
         <v>46947</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
         <v>178</v>
       </c>
@@ -3995,7 +3901,7 @@
         <v>46938</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>179</v>
       </c>
@@ -4012,7 +3918,7 @@
         <v>46551</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>180</v>
       </c>
@@ -4029,7 +3935,7 @@
         <v>46515</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>181</v>
       </c>
@@ -4046,7 +3952,7 @@
         <v>46573</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>182</v>
       </c>
@@ -4063,7 +3969,7 @@
         <v>46573</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
         <v>183</v>
       </c>
@@ -4080,7 +3986,7 @@
         <v>46573</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>184</v>
       </c>
@@ -4097,7 +4003,7 @@
         <v>46566</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>185</v>
       </c>
@@ -4114,7 +4020,7 @@
         <v>46660</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>186</v>
       </c>
@@ -4131,7 +4037,7 @@
         <v>46323</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
         <v>187</v>
       </c>
@@ -4148,7 +4054,7 @@
         <v>46721</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>188</v>
       </c>
@@ -4165,7 +4071,7 @@
         <v>46721</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
         <v>189</v>
       </c>
@@ -4182,7 +4088,7 @@
         <v>46728</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
         <v>190</v>
       </c>
@@ -4199,7 +4105,7 @@
         <v>46728</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
         <v>191</v>
       </c>
@@ -4216,7 +4122,7 @@
         <v>46728</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
         <v>192</v>
       </c>
@@ -4233,7 +4139,7 @@
         <v>46336</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
         <v>193</v>
       </c>
@@ -4250,7 +4156,7 @@
         <v>46338</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
         <v>194</v>
       </c>
@@ -4267,7 +4173,7 @@
         <v>46339</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
         <v>195</v>
       </c>
@@ -4284,7 +4190,7 @@
         <v>46355</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>196</v>
       </c>
@@ -4301,7 +4207,7 @@
         <v>46587</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>197</v>
       </c>
@@ -4318,7 +4224,7 @@
         <v>46285</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>198</v>
       </c>
@@ -4335,7 +4241,7 @@
         <v>46726</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
         <v>199</v>
       </c>
@@ -4352,7 +4258,7 @@
         <v>46490</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>200</v>
       </c>
@@ -4369,7 +4275,7 @@
         <v>47027</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>201</v>
       </c>
@@ -4386,7 +4292,7 @@
         <v>47027</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
         <v>202</v>
       </c>
@@ -4403,7 +4309,7 @@
         <v>47030</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>203</v>
       </c>
@@ -4427,16 +4333,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="5" width="20" customWidth="1"/>
+    <col min="4" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32.1" customHeight="1">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4452,84 +4358,99 @@
       <c r="E1" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>195</v>
       </c>
       <c r="B2" s="2">
-        <v>1006</v>
+        <v>1568</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D2" s="4">
         <v>46240</v>
       </c>
       <c r="E2" s="4">
-        <v>46241</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>46240</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="B3" s="2">
-        <v>1217</v>
+        <v>1335</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="D3" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="E3" s="4">
-        <v>46237</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>46238</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>1205</v>
+        <v>1233</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D4" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="E4" s="4">
-        <v>46237</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>46238</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="B5" s="2">
-        <v>1319</v>
+        <v>1269</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D5" s="4">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="E5" s="4">
-        <v>46236</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>46240</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="B6" s="2">
-        <v>1006</v>
+        <v>1221</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4">
         <v>46235</v>
@@ -4537,175 +4458,408 @@
       <c r="E6" s="4">
         <v>46235</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E7" s="4">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>46237</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="B8" s="2">
-        <v>1263</v>
+        <v>1205</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46237</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46237</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1202</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46235</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46235</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1321</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46266</v>
+      </c>
+      <c r="E10" s="4">
+        <v>46288</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1288</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D8" s="4">
-        <v>46250</v>
-      </c>
-      <c r="E8" s="4">
-        <v>46259</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1302</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="4">
-        <v>46242</v>
-      </c>
-      <c r="E9" s="4">
-        <v>46263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1294</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="4">
-        <v>46228</v>
-      </c>
-      <c r="E10" s="4">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1303</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D11" s="4">
         <v>46235</v>
       </c>
       <c r="E11" s="4">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>46235</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="B12" s="2">
-        <v>1161</v>
+        <v>1319</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D12" s="4">
         <v>46235</v>
       </c>
       <c r="E12" s="4">
-        <v>46254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>46236</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="B13" s="2">
-        <v>1007</v>
+        <v>1263</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="D13" s="4">
         <v>46235</v>
       </c>
       <c r="E13" s="4">
-        <v>46250</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>46235</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2">
-        <v>1567</v>
+        <v>1233</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D14" s="4">
         <v>46235</v>
       </c>
       <c r="E14" s="4">
+        <v>46235</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1006</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46235</v>
+      </c>
+      <c r="E15" s="4">
+        <v>46235</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1210</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="4">
+        <v>46236</v>
+      </c>
+      <c r="E16" s="4">
+        <v>46238</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1263</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="4">
+        <v>46250</v>
+      </c>
+      <c r="E17" s="4">
+        <v>46259</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1302</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="4">
+        <v>46242</v>
+      </c>
+      <c r="E18" s="4">
+        <v>46263</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1294</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="4">
+        <v>46228</v>
+      </c>
+      <c r="E19" s="4">
+        <v>46238</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1303</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="4">
+        <v>46235</v>
+      </c>
+      <c r="E20" s="4">
+        <v>46240</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1200</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="4">
+        <v>46235</v>
+      </c>
+      <c r="E21" s="4">
+        <v>46254</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1161</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="4">
+        <v>46235</v>
+      </c>
+      <c r="E22" s="4">
+        <v>46254</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1007</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4">
+        <v>46235</v>
+      </c>
+      <c r="E23" s="4">
+        <v>46250</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1567</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="4">
+        <v>46235</v>
+      </c>
+      <c r="E24" s="4">
         <v>46243</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="3" t="s">
+      <c r="F24" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B25" s="2">
         <v>1234</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D25" s="4">
         <v>46212</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E25" s="4">
         <v>46240</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="3" t="s">
+      <c r="F25" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B26" s="2">
         <v>1152</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D26" s="4">
         <v>46242</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E26" s="4">
         <v>46254</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -4716,14 +4870,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D181"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="4" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="32.1" customHeight="1">
+    <row r="1" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4731,13 +4885,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -4751,7 +4905,7 @@
         <v>46368</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -4765,7 +4919,7 @@
         <v>49737</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -4779,7 +4933,7 @@
         <v>46258</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4793,7 +4947,7 @@
         <v>46334</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -4807,7 +4961,7 @@
         <v>46242</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -4821,7 +4975,7 @@
         <v>46242</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -4835,7 +4989,7 @@
         <v>46558</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -4849,7 +5003,7 @@
         <v>46372</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -4863,7 +5017,7 @@
         <v>46320</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -4877,7 +5031,7 @@
         <v>46562</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -4891,7 +5045,7 @@
         <v>46328</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -4905,7 +5059,7 @@
         <v>46324</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -4919,7 +5073,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
@@ -4933,7 +5087,7 @@
         <v>46577</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
@@ -4947,7 +5101,7 @@
         <v>46577</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
@@ -4961,7 +5115,7 @@
         <v>46552</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>31</v>
       </c>
@@ -4975,7 +5129,7 @@
         <v>46361</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>32</v>
       </c>
@@ -4989,7 +5143,7 @@
         <v>46311</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>33</v>
       </c>
@@ -5003,7 +5157,7 @@
         <v>46328</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>34</v>
       </c>
@@ -5017,7 +5171,7 @@
         <v>46308</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>35</v>
       </c>
@@ -5031,7 +5185,7 @@
         <v>46403</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>36</v>
       </c>
@@ -5045,7 +5199,7 @@
         <v>49383</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
@@ -5059,7 +5213,7 @@
         <v>49497</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -5073,7 +5227,7 @@
         <v>46533</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>41</v>
       </c>
@@ -5087,7 +5241,7 @@
         <v>48452</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>42</v>
       </c>
@@ -5101,7 +5255,7 @@
         <v>46620</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -5115,7 +5269,7 @@
         <v>46843</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>45</v>
       </c>
@@ -5129,7 +5283,7 @@
         <v>46385</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
@@ -5143,7 +5297,7 @@
         <v>46911</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>47</v>
       </c>
@@ -5157,7 +5311,7 @@
         <v>47735</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>48</v>
       </c>
@@ -5171,7 +5325,7 @@
         <v>47510</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>49</v>
       </c>
@@ -5185,7 +5339,7 @@
         <v>46207</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>50</v>
       </c>
@@ -5199,7 +5353,7 @@
         <v>49319</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>51</v>
       </c>
@@ -5213,7 +5367,7 @@
         <v>48074</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>52</v>
       </c>
@@ -5227,7 +5381,7 @@
         <v>46948</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>53</v>
       </c>
@@ -5241,7 +5395,7 @@
         <v>46948</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>54</v>
       </c>
@@ -5255,7 +5409,7 @@
         <v>46609</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>55</v>
       </c>
@@ -5269,7 +5423,7 @@
         <v>46342</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>56</v>
       </c>
@@ -5283,7 +5437,7 @@
         <v>46733</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>57</v>
       </c>
@@ -5297,7 +5451,7 @@
         <v>47098</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>58</v>
       </c>
@@ -5311,7 +5465,7 @@
         <v>46678</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>59</v>
       </c>
@@ -5325,7 +5479,7 @@
         <v>46863</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>60</v>
       </c>
@@ -5339,7 +5493,7 @@
         <v>47014</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>61</v>
       </c>
@@ -5353,7 +5507,7 @@
         <v>49364</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>63</v>
       </c>
@@ -5367,7 +5521,7 @@
         <v>47527</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>64</v>
       </c>
@@ -5381,7 +5535,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>65</v>
       </c>
@@ -5395,7 +5549,7 @@
         <v>47204</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>66</v>
       </c>
@@ -5409,7 +5563,7 @@
         <v>47364</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>67</v>
       </c>
@@ -5423,7 +5577,7 @@
         <v>46346</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>68</v>
       </c>
@@ -5437,7 +5591,7 @@
         <v>47670</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>69</v>
       </c>
@@ -5451,7 +5605,7 @@
         <v>46390</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>70</v>
       </c>
@@ -5465,7 +5619,7 @@
         <v>46556</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>72</v>
       </c>
@@ -5479,7 +5633,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>73</v>
       </c>
@@ -5493,7 +5647,7 @@
         <v>46327</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>74</v>
       </c>
@@ -5507,7 +5661,7 @@
         <v>46256</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>75</v>
       </c>
@@ -5521,7 +5675,7 @@
         <v>46899</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>77</v>
       </c>
@@ -5535,7 +5689,7 @@
         <v>46460</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>78</v>
       </c>
@@ -5549,7 +5703,7 @@
         <v>46370</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>79</v>
       </c>
@@ -5563,7 +5717,7 @@
         <v>46368</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>80</v>
       </c>
@@ -5577,7 +5731,7 @@
         <v>46394</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>81</v>
       </c>
@@ -5591,7 +5745,7 @@
         <v>46242</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>82</v>
       </c>
@@ -5605,7 +5759,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>83</v>
       </c>
@@ -5619,7 +5773,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>84</v>
       </c>
@@ -5633,7 +5787,7 @@
         <v>46388</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>85</v>
       </c>
@@ -5647,7 +5801,7 @@
         <v>47970</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>86</v>
       </c>
@@ -5661,7 +5815,7 @@
         <v>46783</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>87</v>
       </c>
@@ -5675,7 +5829,7 @@
         <v>47020</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>88</v>
       </c>
@@ -5689,7 +5843,7 @@
         <v>46349</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>89</v>
       </c>
@@ -5703,7 +5857,7 @@
         <v>46349</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>90</v>
       </c>
@@ -5717,7 +5871,7 @@
         <v>46349</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>91</v>
       </c>
@@ -5731,7 +5885,7 @@
         <v>46336</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>92</v>
       </c>
@@ -5745,7 +5899,7 @@
         <v>46383</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>94</v>
       </c>
@@ -5759,7 +5913,7 @@
         <v>46465</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>96</v>
       </c>
@@ -5773,7 +5927,7 @@
         <v>46313</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>97</v>
       </c>
@@ -5787,7 +5941,7 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>98</v>
       </c>
@@ -5801,7 +5955,7 @@
         <v>46315</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>99</v>
       </c>
@@ -5815,7 +5969,7 @@
         <v>46331</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>100</v>
       </c>
@@ -5829,7 +5983,7 @@
         <v>46334</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>101</v>
       </c>
@@ -5843,7 +5997,7 @@
         <v>46396</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>102</v>
       </c>
@@ -5857,7 +6011,7 @@
         <v>46258</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>103</v>
       </c>
@@ -5871,7 +6025,7 @@
         <v>46727</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>104</v>
       </c>
@@ -5885,7 +6039,7 @@
         <v>46867</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>105</v>
       </c>
@@ -5899,7 +6053,7 @@
         <v>46374</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>106</v>
       </c>
@@ -5913,7 +6067,7 @@
         <v>46381</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>107</v>
       </c>
@@ -5927,7 +6081,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>108</v>
       </c>
@@ -5941,7 +6095,7 @@
         <v>46321</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>109</v>
       </c>
@@ -5955,7 +6109,7 @@
         <v>47891</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>110</v>
       </c>
@@ -5969,7 +6123,7 @@
         <v>46251</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>111</v>
       </c>
@@ -5983,7 +6137,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>112</v>
       </c>
@@ -5997,7 +6151,7 @@
         <v>46335</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>113</v>
       </c>
@@ -6011,7 +6165,7 @@
         <v>46335</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>114</v>
       </c>
@@ -6025,7 +6179,7 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>115</v>
       </c>
@@ -6039,7 +6193,7 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>116</v>
       </c>
@@ -6053,7 +6207,7 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>117</v>
       </c>
@@ -6067,7 +6221,7 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>118</v>
       </c>
@@ -6081,7 +6235,7 @@
         <v>46552</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>119</v>
       </c>
@@ -6095,7 +6249,7 @@
         <v>46344</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>120</v>
       </c>
@@ -6109,7 +6263,7 @@
         <v>47252</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>121</v>
       </c>
@@ -6123,7 +6277,7 @@
         <v>46409</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>122</v>
       </c>
@@ -6137,7 +6291,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>123</v>
       </c>
@@ -6151,7 +6305,7 @@
         <v>46594</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>124</v>
       </c>
@@ -6165,7 +6319,7 @@
         <v>46404</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>125</v>
       </c>
@@ -6179,7 +6333,7 @@
         <v>46404</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>126</v>
       </c>
@@ -6193,7 +6347,7 @@
         <v>46404</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>127</v>
       </c>
@@ -6207,7 +6361,7 @@
         <v>46404</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>128</v>
       </c>
@@ -6221,7 +6375,7 @@
         <v>46393</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>129</v>
       </c>
@@ -6235,7 +6389,7 @@
         <v>46252</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>131</v>
       </c>
@@ -6249,7 +6403,7 @@
         <v>46569</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>132</v>
       </c>
@@ -6263,7 +6417,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>133</v>
       </c>
@@ -6277,7 +6431,7 @@
         <v>46296</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>134</v>
       </c>
@@ -6291,7 +6445,7 @@
         <v>46414</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>135</v>
       </c>
@@ -6305,7 +6459,7 @@
         <v>46587</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>136</v>
       </c>
@@ -6319,7 +6473,7 @@
         <v>46308</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>137</v>
       </c>
@@ -6333,7 +6487,7 @@
         <v>46310</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>138</v>
       </c>
@@ -6347,7 +6501,7 @@
         <v>46226</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>139</v>
       </c>
@@ -6361,7 +6515,7 @@
         <v>46456</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>140</v>
       </c>
@@ -6375,7 +6529,7 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>141</v>
       </c>
@@ -6389,7 +6543,7 @@
         <v>46302</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>142</v>
       </c>
@@ -6403,7 +6557,7 @@
         <v>46355</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>143</v>
       </c>
@@ -6417,7 +6571,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>144</v>
       </c>
@@ -6431,7 +6585,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>145</v>
       </c>
@@ -6445,7 +6599,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>146</v>
       </c>
@@ -6459,7 +6613,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>147</v>
       </c>
@@ -6473,7 +6627,7 @@
         <v>46316</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>148</v>
       </c>
@@ -6487,7 +6641,7 @@
         <v>46316</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>149</v>
       </c>
@@ -6501,7 +6655,7 @@
         <v>46534</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>150</v>
       </c>
@@ -6515,7 +6669,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>151</v>
       </c>
@@ -6529,7 +6683,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>152</v>
       </c>
@@ -6543,7 +6697,7 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>153</v>
       </c>
@@ -6557,7 +6711,7 @@
         <v>46582</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>154</v>
       </c>
@@ -6571,7 +6725,7 @@
         <v>46584</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>155</v>
       </c>
@@ -6585,7 +6739,7 @@
         <v>47903</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>156</v>
       </c>
@@ -6599,7 +6753,7 @@
         <v>46983</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>157</v>
       </c>
@@ -6613,7 +6767,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>158</v>
       </c>
@@ -6627,7 +6781,7 @@
         <v>46247</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>159</v>
       </c>
@@ -6641,7 +6795,7 @@
         <v>46351</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>160</v>
       </c>
@@ -6655,7 +6809,7 @@
         <v>46324</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>161</v>
       </c>
@@ -6669,7 +6823,7 @@
         <v>46263</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>162</v>
       </c>
@@ -6683,7 +6837,7 @@
         <v>46399</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>163</v>
       </c>
@@ -6697,7 +6851,7 @@
         <v>46373</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>164</v>
       </c>
@@ -6711,7 +6865,7 @@
         <v>46263</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>165</v>
       </c>
@@ -6725,7 +6879,7 @@
         <v>46263</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>166</v>
       </c>
@@ -6739,7 +6893,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>167</v>
       </c>
@@ -6753,7 +6907,7 @@
         <v>46368</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>168</v>
       </c>
@@ -6767,7 +6921,7 @@
         <v>46226</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>169</v>
       </c>
@@ -6781,7 +6935,7 @@
         <v>46319</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>170</v>
       </c>
@@ -6795,7 +6949,7 @@
         <v>46413</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>171</v>
       </c>
@@ -6809,7 +6963,7 @@
         <v>46408</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>172</v>
       </c>
@@ -6823,7 +6977,7 @@
         <v>46373</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>173</v>
       </c>
@@ -6837,7 +6991,7 @@
         <v>46370</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>174</v>
       </c>
@@ -6851,7 +7005,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>175</v>
       </c>
@@ -6865,7 +7019,7 @@
         <v>46389</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>176</v>
       </c>
@@ -6879,7 +7033,7 @@
         <v>46319</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>177</v>
       </c>
@@ -6893,7 +7047,7 @@
         <v>46333</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>178</v>
       </c>
@@ -6907,7 +7061,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>179</v>
       </c>
@@ -6921,7 +7075,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>180</v>
       </c>
@@ -6935,7 +7089,7 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>181</v>
       </c>
@@ -6949,7 +7103,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>182</v>
       </c>
@@ -6963,7 +7117,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>183</v>
       </c>
@@ -6977,7 +7131,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>184</v>
       </c>
@@ -6991,7 +7145,7 @@
         <v>46379</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>185</v>
       </c>
@@ -7005,7 +7159,7 @@
         <v>46303</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>186</v>
       </c>
@@ -7019,7 +7173,7 @@
         <v>46330</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>187</v>
       </c>
@@ -7033,7 +7187,7 @@
         <v>46244</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>188</v>
       </c>
@@ -7047,7 +7201,7 @@
         <v>46244</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>189</v>
       </c>
@@ -7061,7 +7215,7 @@
         <v>46252</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>190</v>
       </c>
@@ -7075,7 +7229,7 @@
         <v>46342</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>191</v>
       </c>
@@ -7089,7 +7243,7 @@
         <v>46252</v>
       </c>
     </row>
-    <row r="170" spans="1:4">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>192</v>
       </c>
@@ -7103,7 +7257,7 @@
         <v>46465</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>193</v>
       </c>
@@ -7117,7 +7271,7 @@
         <v>46368</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>194</v>
       </c>
@@ -7131,7 +7285,7 @@
         <v>46353</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>195</v>
       </c>
@@ -7145,7 +7299,7 @@
         <v>46361</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>196</v>
       </c>
@@ -7159,7 +7313,7 @@
         <v>46899</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>197</v>
       </c>
@@ -7173,7 +7327,7 @@
         <v>46397</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>198</v>
       </c>
@@ -7187,7 +7341,7 @@
         <v>46344</v>
       </c>
     </row>
-    <row r="177" spans="1:4">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>199</v>
       </c>
@@ -7201,7 +7355,7 @@
         <v>46307</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>200</v>
       </c>
@@ -7215,7 +7369,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="179" spans="1:4">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>201</v>
       </c>
@@ -7229,7 +7383,7 @@
         <v>46334</v>
       </c>
     </row>
-    <row r="180" spans="1:4">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>202</v>
       </c>
@@ -7243,7 +7397,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="181" spans="1:4">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>203</v>
       </c>
@@ -7264,153 +7418,176 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:A38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18" customHeight="1">
+    <row r="1" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -7421,7 +7598,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G181"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -7432,7 +7609,7 @@
     <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -7440,3950 +7617,2360 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="9">
         <v>1004</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
       <c r="E2" s="10"/>
-      <c r="F2" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="G2" s="11">
-        <v>27315</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="9">
         <v>1005</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
       <c r="E3" s="10"/>
-      <c r="F3" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G3" s="11">
-        <v>34516</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="9">
         <v>1006</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>258</v>
-      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
       <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G4" s="11">
-        <v>31292</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="9">
         <v>1007</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>259</v>
-      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G5" s="11">
-        <v>32874</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="9">
         <v>1008</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G6" s="11">
-        <v>31413</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="9">
         <v>1009</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G7" s="11">
-        <v>30792</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="9">
         <v>1010</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>260</v>
-      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="G8" s="11">
-        <v>27230</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="9">
         <v>1012</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="G9" s="11">
-        <v>35290</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B10" s="9">
         <v>1103</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G10" s="11">
-        <v>27505</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="9">
         <v>1104</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G11" s="11">
-        <v>30397</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="9">
         <v>1106</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G12" s="11">
-        <v>27435</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="9">
         <v>1107</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G13" s="11">
-        <v>32874</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="9">
         <v>1108</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="10"/>
-      <c r="F14" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G14" s="11">
-        <v>34440</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="9">
         <v>1111</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G15" s="11">
-        <v>35483</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="9">
         <v>1112</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G16" s="11">
-        <v>35796</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="9">
         <v>1115</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="10"/>
-      <c r="F17" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="G17" s="11">
-        <v>31778</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B18" s="9">
         <v>1117</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="10"/>
-      <c r="F18" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G18" s="11">
-        <v>34444</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="9">
         <v>1120</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="10"/>
-      <c r="F19" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G19" s="11">
-        <v>33521</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="9">
         <v>1121</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
       <c r="E20" s="10"/>
-      <c r="F20" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G20" s="11">
-        <v>27388</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B21" s="9">
         <v>1122</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
       <c r="E21" s="10"/>
-      <c r="F21" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G21" s="11">
-        <v>35596</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="9">
         <v>1123</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
       <c r="E22" s="10"/>
-      <c r="F22" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G22" s="11">
-        <v>35065</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="9">
         <v>1152</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G23" s="11">
-        <v>33534</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B24" s="9">
         <v>1153</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>265</v>
-      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G24" s="11">
-        <v>34913</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B25" s="9">
         <v>1157</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G25" s="11">
-        <v>35162</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B26" s="9">
         <v>1159</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G26" s="11">
-        <v>32610</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B27" s="9">
         <v>1161</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G27" s="11">
-        <v>30582</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B28" s="9">
         <v>1162</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G28" s="11">
-        <v>37700</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>45</v>
       </c>
       <c r="B29" s="9">
         <v>1166</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G29" s="11">
-        <v>33711</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="9">
         <v>1167</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
       <c r="E30" s="10"/>
-      <c r="F30" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G30" s="11">
-        <v>35776</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B31" s="9">
         <v>1168</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
       <c r="E31" s="10"/>
-      <c r="F31" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G31" s="11">
-        <v>35547</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>48</v>
       </c>
       <c r="B32" s="9">
         <v>1170</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
       <c r="E32" s="10"/>
-      <c r="F32" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G32" s="11">
-        <v>36869</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B33" s="9">
         <v>1175</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
       <c r="E33" s="10"/>
-      <c r="F33" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G33" s="11">
-        <v>31690</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="9">
         <v>1178</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
       <c r="E34" s="10"/>
-      <c r="F34" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G34" s="11">
-        <v>34315</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B35" s="9">
         <v>1180</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
       <c r="E35" s="10"/>
-      <c r="F35" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G35" s="11">
-        <v>33420</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B36" s="9">
         <v>1181</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
       <c r="E36" s="10"/>
-      <c r="F36" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G36" s="11">
-        <v>37799</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="9">
         <v>1182</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
       <c r="E37" s="10"/>
-      <c r="F37" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G37" s="11">
-        <v>37799</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B38" s="9">
         <v>1183</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
       <c r="E38" s="10"/>
-      <c r="F38" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G38" s="11">
-        <v>35293</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B39" s="9">
         <v>1185</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G39" s="11">
-        <v>34811</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B40" s="9">
         <v>1192</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>268</v>
-      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
       <c r="E40" s="10"/>
-      <c r="F40" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G40" s="11">
-        <v>37877</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B41" s="9">
         <v>1198</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
       <c r="E41" s="10"/>
-      <c r="F41" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G41" s="11">
-        <v>34946</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>58</v>
       </c>
       <c r="B42" s="9">
         <v>1199</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
       <c r="E42" s="10"/>
-      <c r="F42" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G42" s="11">
-        <v>35176</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B43" s="9">
         <v>1200</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
       <c r="E43" s="10"/>
-      <c r="F43" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G43" s="11">
-        <v>35051</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>60</v>
       </c>
       <c r="B44" s="9">
         <v>1202</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>269</v>
-      </c>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
       <c r="E44" s="10"/>
-      <c r="F44" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G44" s="11">
-        <v>36613</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>61</v>
       </c>
       <c r="B45" s="9">
         <v>1205</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
       <c r="E45" s="10"/>
-      <c r="F45" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G45" s="11">
-        <v>33519</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B46" s="9">
         <v>1206</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>269</v>
-      </c>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
       <c r="E46" s="10"/>
-      <c r="F46" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G46" s="11">
-        <v>36434</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>64</v>
       </c>
       <c r="B47" s="9">
         <v>1207</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>260</v>
-      </c>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
       <c r="E47" s="10"/>
-      <c r="F47" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G47" s="11">
-        <v>34045</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B48" s="9">
         <v>1210</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
       <c r="E48" s="10"/>
-      <c r="F48" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G48" s="11">
-        <v>36458</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>66</v>
       </c>
       <c r="B49" s="9">
         <v>1217</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>260</v>
-      </c>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
       <c r="E49" s="10"/>
-      <c r="F49" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G49" s="11">
-        <v>36573</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>67</v>
       </c>
       <c r="B50" s="9">
         <v>1219</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
       <c r="E50" s="10"/>
-      <c r="F50" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G50" s="11">
-        <v>35431</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>68</v>
       </c>
       <c r="B51" s="9">
         <v>1221</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
       <c r="E51" s="10"/>
-      <c r="F51" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G51" s="11">
-        <v>36759</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>69</v>
       </c>
       <c r="B52" s="9">
         <v>1222</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
       <c r="E52" s="10"/>
-      <c r="F52" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="G52" s="11">
-        <v>32573</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>70</v>
       </c>
       <c r="B53" s="9">
         <v>1224</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>271</v>
-      </c>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
       <c r="E53" s="10"/>
-      <c r="F53" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G53" s="11">
-        <v>37055</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>72</v>
       </c>
       <c r="B54" s="9">
         <v>1226</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
       <c r="E54" s="10"/>
-      <c r="F54" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="G54" s="11">
-        <v>28546</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B55" s="9">
         <v>1229</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
       <c r="E55" s="10"/>
-      <c r="F55" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="G55" s="11">
-        <v>34271</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B56" s="9">
         <v>1230</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
       <c r="E56" s="10"/>
-      <c r="F56" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G56" s="11">
-        <v>35797</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
         <v>75</v>
       </c>
       <c r="B57" s="9">
         <v>1232</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
       <c r="E57" s="10"/>
-      <c r="F57" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="G57" s="11">
-        <v>37863</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
         <v>77</v>
       </c>
       <c r="B58" s="9">
         <v>1233</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
       <c r="E58" s="10"/>
-      <c r="F58" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="G58" s="11">
-        <v>37935</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
         <v>78</v>
       </c>
       <c r="B59" s="9">
         <v>1234</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
       <c r="E59" s="10"/>
-      <c r="F59" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="G59" s="11">
-        <v>34360</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
         <v>79</v>
       </c>
       <c r="B60" s="9">
         <v>1235</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
       <c r="E60" s="10"/>
-      <c r="F60" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G60" s="11">
-        <v>37095</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
         <v>80</v>
       </c>
       <c r="B61" s="9">
         <v>1237</v>
       </c>
-      <c r="C61" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>272</v>
-      </c>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
       <c r="E61" s="10"/>
-      <c r="F61" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G61" s="11">
-        <v>32856</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
         <v>81</v>
       </c>
       <c r="B62" s="9">
         <v>1239</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
       <c r="E62" s="10"/>
-      <c r="F62" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G62" s="11">
-        <v>34963</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
         <v>82</v>
       </c>
       <c r="B63" s="9">
         <v>1240</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
       <c r="E63" s="10"/>
-      <c r="F63" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G63" s="11">
-        <v>37346</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>83</v>
       </c>
       <c r="B64" s="9">
         <v>1241</v>
       </c>
-      <c r="C64" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
       <c r="E64" s="10"/>
-      <c r="F64" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G64" s="11">
-        <v>37445</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
         <v>84</v>
       </c>
       <c r="B65" s="9">
         <v>1242</v>
       </c>
-      <c r="C65" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
       <c r="E65" s="10"/>
-      <c r="F65" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G65" s="11">
-        <v>33618</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="F65" s="10"/>
+      <c r="G65" s="10"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
         <v>85</v>
       </c>
       <c r="B66" s="9">
         <v>1243</v>
       </c>
-      <c r="C66" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
       <c r="E66" s="10"/>
-      <c r="F66" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G66" s="11">
-        <v>38948</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="F66" s="10"/>
+      <c r="G66" s="10"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B67" s="9">
         <v>1244</v>
       </c>
-      <c r="C67" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
       <c r="E67" s="10"/>
-      <c r="F67" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G67" s="11">
-        <v>38088</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
         <v>87</v>
       </c>
       <c r="B68" s="9">
         <v>1245</v>
       </c>
-      <c r="C68" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
       <c r="E68" s="10"/>
-      <c r="F68" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G68" s="11">
-        <v>38200</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
         <v>88</v>
       </c>
       <c r="B69" s="9">
         <v>1246</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>268</v>
-      </c>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
       <c r="E69" s="10"/>
-      <c r="F69" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G69" s="11">
-        <v>34587</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="F69" s="10"/>
+      <c r="G69" s="10"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
         <v>89</v>
       </c>
       <c r="B70" s="9">
         <v>1247</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
       <c r="E70" s="10"/>
-      <c r="F70" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G70" s="11">
-        <v>35766</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+      <c r="F70" s="10"/>
+      <c r="G70" s="10"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
         <v>90</v>
       </c>
       <c r="B71" s="9">
         <v>1249</v>
       </c>
-      <c r="C71" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
       <c r="E71" s="10"/>
-      <c r="F71" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G71" s="11">
-        <v>37806</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
         <v>91</v>
       </c>
       <c r="B72" s="9">
         <v>1250</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
       <c r="E72" s="10"/>
-      <c r="F72" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G72" s="11">
-        <v>36996</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="F72" s="10"/>
+      <c r="G72" s="10"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
         <v>92</v>
       </c>
       <c r="B73" s="9">
         <v>1252</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="C73" s="10"/>
+      <c r="D73" s="10"/>
       <c r="E73" s="10"/>
-      <c r="F73" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G73" s="11">
-        <v>30682</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="F73" s="10"/>
+      <c r="G73" s="10"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
         <v>94</v>
       </c>
       <c r="B74" s="9">
         <v>1253</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
       <c r="E74" s="10"/>
-      <c r="F74" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="G74" s="11">
-        <v>35912</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="F74" s="10"/>
+      <c r="G74" s="10"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
         <v>96</v>
       </c>
       <c r="B75" s="9">
         <v>1254</v>
       </c>
-      <c r="C75" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="C75" s="10"/>
+      <c r="D75" s="10"/>
       <c r="E75" s="10"/>
-      <c r="F75" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G75" s="11">
-        <v>36811</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+      <c r="F75" s="10"/>
+      <c r="G75" s="10"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
         <v>97</v>
       </c>
       <c r="B76" s="9">
         <v>1255</v>
       </c>
-      <c r="C76" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
       <c r="E76" s="10"/>
-      <c r="F76" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G76" s="11">
-        <v>32487</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+      <c r="F76" s="10"/>
+      <c r="G76" s="10"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B77" s="9">
         <v>1256</v>
       </c>
-      <c r="C77" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C77" s="10"/>
+      <c r="D77" s="10"/>
       <c r="E77" s="10"/>
-      <c r="F77" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G77" s="11">
-        <v>31238</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+      <c r="F77" s="10"/>
+      <c r="G77" s="10"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
         <v>99</v>
       </c>
       <c r="B78" s="9">
         <v>1258</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C78" s="10"/>
+      <c r="D78" s="10"/>
       <c r="E78" s="10"/>
-      <c r="F78" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G78" s="11">
-        <v>34517</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+      <c r="F78" s="10"/>
+      <c r="G78" s="10"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
         <v>100</v>
       </c>
       <c r="B79" s="9">
         <v>1259</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C79" s="10"/>
+      <c r="D79" s="10"/>
       <c r="E79" s="10"/>
-      <c r="F79" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G79" s="11">
-        <v>28980</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="F79" s="10"/>
+      <c r="G79" s="10"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
         <v>101</v>
       </c>
       <c r="B80" s="9">
         <v>1262</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>271</v>
-      </c>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
       <c r="E80" s="10"/>
-      <c r="F80" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="G80" s="11">
-        <v>34893</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="F80" s="10"/>
+      <c r="G80" s="10"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
         <v>102</v>
       </c>
       <c r="B81" s="9">
         <v>1263</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>271</v>
-      </c>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
       <c r="E81" s="10"/>
-      <c r="F81" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="G81" s="11">
-        <v>35632</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+      <c r="F81" s="10"/>
+      <c r="G81" s="10"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="9" t="s">
         <v>103</v>
       </c>
       <c r="B82" s="9">
         <v>1264</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
       <c r="E82" s="10"/>
-      <c r="F82" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G82" s="11">
-        <v>37824</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="9" t="s">
         <v>104</v>
       </c>
       <c r="B83" s="9">
         <v>1266</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C83" s="10"/>
+      <c r="D83" s="10"/>
       <c r="E83" s="10"/>
-      <c r="F83" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G83" s="11">
-        <v>38042</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+      <c r="F83" s="10"/>
+      <c r="G83" s="10"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
         <v>105</v>
       </c>
       <c r="B84" s="9">
         <v>1267</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="C84" s="10"/>
+      <c r="D84" s="10"/>
       <c r="E84" s="10"/>
-      <c r="F84" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G84" s="11">
-        <v>34943</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+      <c r="F84" s="10"/>
+      <c r="G84" s="10"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="9" t="s">
         <v>106</v>
       </c>
       <c r="B85" s="9">
         <v>1268</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C85" s="10"/>
+      <c r="D85" s="10"/>
       <c r="E85" s="10"/>
-      <c r="F85" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G85" s="11">
-        <v>35472</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="F85" s="10"/>
+      <c r="G85" s="10"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="9" t="s">
         <v>107</v>
       </c>
       <c r="B86" s="9">
         <v>1269</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D86" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="C86" s="10"/>
+      <c r="D86" s="10"/>
       <c r="E86" s="10"/>
-      <c r="F86" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="G86" s="11">
-        <v>35714</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="F86" s="10"/>
+      <c r="G86" s="10"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
         <v>108</v>
       </c>
       <c r="B87" s="9">
         <v>1270</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>273</v>
-      </c>
+      <c r="C87" s="10"/>
+      <c r="D87" s="10"/>
       <c r="E87" s="10"/>
-      <c r="F87" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G87" s="11">
-        <v>35077</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+      <c r="F87" s="10"/>
+      <c r="G87" s="10"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
         <v>109</v>
       </c>
       <c r="B88" s="9">
         <v>1272</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C88" s="10"/>
+      <c r="D88" s="10"/>
       <c r="E88" s="10"/>
-      <c r="F88" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G88" s="11">
-        <v>39046</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+      <c r="F88" s="10"/>
+      <c r="G88" s="10"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
         <v>110</v>
       </c>
       <c r="B89" s="9">
         <v>1273</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D89" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C89" s="10"/>
+      <c r="D89" s="10"/>
       <c r="E89" s="10"/>
-      <c r="F89" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G89" s="11">
-        <v>35023</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+      <c r="F89" s="10"/>
+      <c r="G89" s="10"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
         <v>111</v>
       </c>
       <c r="B90" s="9">
         <v>1274</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C90" s="10"/>
+      <c r="D90" s="10"/>
       <c r="E90" s="10"/>
-      <c r="F90" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G90" s="11">
-        <v>35115</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+      <c r="F90" s="10"/>
+      <c r="G90" s="10"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="9" t="s">
         <v>112</v>
       </c>
       <c r="B91" s="9">
         <v>1276</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D91" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="C91" s="10"/>
+      <c r="D91" s="10"/>
       <c r="E91" s="10"/>
-      <c r="F91" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G91" s="11">
-        <v>32143</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+      <c r="F91" s="10"/>
+      <c r="G91" s="10"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
         <v>113</v>
       </c>
       <c r="B92" s="9">
         <v>1277</v>
       </c>
-      <c r="C92" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10"/>
       <c r="E92" s="10"/>
-      <c r="F92" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G92" s="11">
-        <v>36892</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+      <c r="F92" s="10"/>
+      <c r="G92" s="10"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="9" t="s">
         <v>114</v>
       </c>
       <c r="B93" s="9">
         <v>1279</v>
       </c>
-      <c r="C93" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C93" s="10"/>
+      <c r="D93" s="10"/>
       <c r="E93" s="10"/>
-      <c r="F93" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="G93" s="11">
-        <v>33092</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+      <c r="F93" s="10"/>
+      <c r="G93" s="10"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="9" t="s">
         <v>115</v>
       </c>
       <c r="B94" s="9">
         <v>1280</v>
       </c>
-      <c r="C94" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C94" s="10"/>
+      <c r="D94" s="10"/>
       <c r="E94" s="10"/>
-      <c r="F94" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="G94" s="11">
-        <v>34347</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+      <c r="F94" s="10"/>
+      <c r="G94" s="10"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="9" t="s">
         <v>116</v>
       </c>
       <c r="B95" s="9">
         <v>1281</v>
       </c>
-      <c r="C95" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C95" s="10"/>
+      <c r="D95" s="10"/>
       <c r="E95" s="10"/>
-      <c r="F95" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="G95" s="11">
-        <v>32939</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+      <c r="F95" s="10"/>
+      <c r="G95" s="10"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="9" t="s">
         <v>117</v>
       </c>
       <c r="B96" s="9">
         <v>1282</v>
       </c>
-      <c r="C96" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C96" s="10"/>
+      <c r="D96" s="10"/>
       <c r="E96" s="10"/>
-      <c r="F96" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="G96" s="11">
-        <v>33884</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+      <c r="F96" s="10"/>
+      <c r="G96" s="10"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B97" s="9">
         <v>1283</v>
       </c>
-      <c r="C97" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C97" s="10"/>
+      <c r="D97" s="10"/>
       <c r="E97" s="10"/>
-      <c r="F97" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G97" s="11">
-        <v>34541</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
+      <c r="F97" s="10"/>
+      <c r="G97" s="10"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="9" t="s">
         <v>119</v>
       </c>
       <c r="B98" s="9">
         <v>1285</v>
       </c>
-      <c r="C98" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C98" s="10"/>
+      <c r="D98" s="10"/>
       <c r="E98" s="10"/>
-      <c r="F98" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G98" s="11">
-        <v>36854</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
+      <c r="F98" s="10"/>
+      <c r="G98" s="10"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="9" t="s">
         <v>120</v>
       </c>
       <c r="B99" s="9">
         <v>1286</v>
       </c>
-      <c r="C99" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C99" s="10"/>
+      <c r="D99" s="10"/>
       <c r="E99" s="10"/>
-      <c r="F99" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G99" s="11">
-        <v>35703</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
+      <c r="F99" s="10"/>
+      <c r="G99" s="10"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
         <v>121</v>
       </c>
       <c r="B100" s="9">
         <v>1288</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D100" s="10" t="s">
-        <v>271</v>
-      </c>
+      <c r="C100" s="10"/>
+      <c r="D100" s="10"/>
       <c r="E100" s="10"/>
-      <c r="F100" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="G100" s="11">
-        <v>35139</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
+      <c r="F100" s="10"/>
+      <c r="G100" s="10"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="9" t="s">
         <v>122</v>
       </c>
       <c r="B101" s="9">
         <v>1289</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D101" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C101" s="10"/>
+      <c r="D101" s="10"/>
       <c r="E101" s="10"/>
-      <c r="F101" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G101" s="11">
-        <v>33116</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
+      <c r="F101" s="10"/>
+      <c r="G101" s="10"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
         <v>123</v>
       </c>
       <c r="B102" s="9">
         <v>1294</v>
       </c>
-      <c r="C102" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D102" s="10" t="s">
-        <v>271</v>
-      </c>
+      <c r="C102" s="10"/>
+      <c r="D102" s="10"/>
       <c r="E102" s="10"/>
-      <c r="F102" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="G102" s="11">
-        <v>37855</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+      <c r="F102" s="10"/>
+      <c r="G102" s="10"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
         <v>124</v>
       </c>
       <c r="B103" s="9">
         <v>1295</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C103" s="10"/>
+      <c r="D103" s="10"/>
       <c r="E103" s="10"/>
-      <c r="F103" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G103" s="11">
-        <v>35520</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+      <c r="F103" s="10"/>
+      <c r="G103" s="10"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
         <v>125</v>
       </c>
       <c r="B104" s="9">
         <v>1296</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C104" s="10"/>
+      <c r="D104" s="10"/>
       <c r="E104" s="10"/>
-      <c r="F104" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G104" s="11">
-        <v>34867</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
+      <c r="F104" s="10"/>
+      <c r="G104" s="10"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
         <v>126</v>
       </c>
       <c r="B105" s="9">
         <v>1297</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="C105" s="10"/>
+      <c r="D105" s="10"/>
       <c r="E105" s="10"/>
-      <c r="F105" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G105" s="11">
-        <v>36932</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+      <c r="F105" s="10"/>
+      <c r="G105" s="10"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
         <v>127</v>
       </c>
       <c r="B106" s="9">
         <v>1298</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D106" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C106" s="10"/>
+      <c r="D106" s="10"/>
       <c r="E106" s="10"/>
-      <c r="F106" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G106" s="11">
-        <v>36258</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+      <c r="F106" s="10"/>
+      <c r="G106" s="10"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="9" t="s">
         <v>128</v>
       </c>
       <c r="B107" s="9">
         <v>1299</v>
       </c>
-      <c r="C107" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D107" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C107" s="10"/>
+      <c r="D107" s="10"/>
       <c r="E107" s="10"/>
-      <c r="F107" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G107" s="11">
-        <v>33512</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+      <c r="F107" s="10"/>
+      <c r="G107" s="10"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
         <v>129</v>
       </c>
       <c r="B108" s="9">
         <v>1301</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D108" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C108" s="10"/>
+      <c r="D108" s="10"/>
       <c r="E108" s="10"/>
-      <c r="F108" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G108" s="11">
-        <v>29952</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+      <c r="F108" s="10"/>
+      <c r="G108" s="10"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="9" t="s">
         <v>131</v>
       </c>
       <c r="B109" s="9">
         <v>1302</v>
       </c>
-      <c r="C109" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D109" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C109" s="10"/>
+      <c r="D109" s="10"/>
       <c r="E109" s="10"/>
-      <c r="F109" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G109" s="11">
-        <v>26299</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+      <c r="F109" s="10"/>
+      <c r="G109" s="10"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
         <v>132</v>
       </c>
       <c r="B110" s="9">
         <v>1303</v>
       </c>
-      <c r="C110" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D110" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C110" s="10"/>
+      <c r="D110" s="10"/>
       <c r="E110" s="10"/>
-      <c r="F110" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G110" s="11">
-        <v>24838</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
+      <c r="F110" s="10"/>
+      <c r="G110" s="10"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="9" t="s">
         <v>133</v>
       </c>
       <c r="B111" s="9">
         <v>1304</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D111" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C111" s="10"/>
+      <c r="D111" s="10"/>
       <c r="E111" s="10"/>
-      <c r="F111" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G111" s="11">
-        <v>32360</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+      <c r="F111" s="10"/>
+      <c r="G111" s="10"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
         <v>134</v>
       </c>
       <c r="B112" s="9">
         <v>1306</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D112" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C112" s="10"/>
+      <c r="D112" s="10"/>
       <c r="E112" s="10"/>
-      <c r="F112" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G112" s="11">
-        <v>34335</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+      <c r="F112" s="10"/>
+      <c r="G112" s="10"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="9" t="s">
         <v>135</v>
       </c>
       <c r="B113" s="9">
         <v>1309</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D113" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C113" s="10"/>
+      <c r="D113" s="10"/>
       <c r="E113" s="10"/>
-      <c r="F113" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G113" s="11">
-        <v>31413</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+      <c r="F113" s="10"/>
+      <c r="G113" s="10"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
         <v>136</v>
       </c>
       <c r="B114" s="9">
         <v>1315</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D114" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="C114" s="10"/>
+      <c r="D114" s="10"/>
       <c r="E114" s="10"/>
-      <c r="F114" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G114" s="11">
-        <v>31668</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+      <c r="F114" s="10"/>
+      <c r="G114" s="10"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="9" t="s">
         <v>137</v>
       </c>
       <c r="B115" s="9">
         <v>1316</v>
       </c>
-      <c r="C115" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D115" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C115" s="10"/>
+      <c r="D115" s="10"/>
       <c r="E115" s="10"/>
-      <c r="F115" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G115" s="11">
-        <v>36661</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+      <c r="F115" s="10"/>
+      <c r="G115" s="10"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
         <v>138</v>
       </c>
       <c r="B116" s="9">
         <v>1318</v>
       </c>
-      <c r="C116" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D116" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C116" s="10"/>
+      <c r="D116" s="10"/>
       <c r="E116" s="10"/>
-      <c r="F116" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G116" s="11">
-        <v>32973</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+      <c r="F116" s="10"/>
+      <c r="G116" s="10"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="9" t="s">
         <v>139</v>
       </c>
       <c r="B117" s="9">
         <v>1319</v>
       </c>
-      <c r="C117" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D117" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C117" s="10"/>
+      <c r="D117" s="10"/>
       <c r="E117" s="10"/>
-      <c r="F117" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G117" s="11">
-        <v>31413</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+      <c r="F117" s="10"/>
+      <c r="G117" s="10"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
         <v>140</v>
       </c>
       <c r="B118" s="9">
         <v>1320</v>
       </c>
-      <c r="C118" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D118" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C118" s="10"/>
+      <c r="D118" s="10"/>
       <c r="E118" s="10"/>
-      <c r="F118" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G118" s="11">
-        <v>31778</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+      <c r="F118" s="10"/>
+      <c r="G118" s="10"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="9" t="s">
         <v>141</v>
       </c>
       <c r="B119" s="9">
         <v>1321</v>
       </c>
-      <c r="C119" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D119" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C119" s="10"/>
+      <c r="D119" s="10"/>
       <c r="E119" s="10"/>
-      <c r="F119" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="G119" s="11">
-        <v>33061</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+      <c r="F119" s="10"/>
+      <c r="G119" s="10"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
         <v>142</v>
       </c>
       <c r="B120" s="9">
         <v>1323</v>
       </c>
-      <c r="C120" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C120" s="10"/>
+      <c r="D120" s="10"/>
       <c r="E120" s="10"/>
-      <c r="F120" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G120" s="11">
-        <v>32590</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+      <c r="F120" s="10"/>
+      <c r="G120" s="10"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
         <v>143</v>
       </c>
       <c r="B121" s="9">
         <v>1324</v>
       </c>
-      <c r="C121" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C121" s="10"/>
+      <c r="D121" s="10"/>
       <c r="E121" s="10"/>
-      <c r="F121" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G121" s="11">
-        <v>27242</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+      <c r="F121" s="10"/>
+      <c r="G121" s="10"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="9" t="s">
         <v>144</v>
       </c>
       <c r="B122" s="9">
         <v>1325</v>
       </c>
-      <c r="C122" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C122" s="10"/>
+      <c r="D122" s="10"/>
       <c r="E122" s="10"/>
-      <c r="F122" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G122" s="11">
-        <v>29952</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+      <c r="F122" s="10"/>
+      <c r="G122" s="10"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="9" t="s">
         <v>145</v>
       </c>
       <c r="B123" s="9">
         <v>1326</v>
       </c>
-      <c r="C123" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D123" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C123" s="10"/>
+      <c r="D123" s="10"/>
       <c r="E123" s="10"/>
-      <c r="F123" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G123" s="11">
-        <v>28932</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+      <c r="F123" s="10"/>
+      <c r="G123" s="10"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="9" t="s">
         <v>146</v>
       </c>
       <c r="B124" s="9">
         <v>1330</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>263</v>
-      </c>
+      <c r="C124" s="10"/>
+      <c r="D124" s="10"/>
       <c r="E124" s="10"/>
-      <c r="F124" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G124" s="11">
-        <v>31413</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+      <c r="F124" s="10"/>
+      <c r="G124" s="10"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
         <v>147</v>
       </c>
       <c r="B125" s="9">
         <v>1331</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="C125" s="10"/>
+      <c r="D125" s="10"/>
       <c r="E125" s="10"/>
-      <c r="F125" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G125" s="11">
-        <v>36180</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+      <c r="F125" s="10"/>
+      <c r="G125" s="10"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="9" t="s">
         <v>148</v>
       </c>
       <c r="B126" s="9">
         <v>1332</v>
       </c>
-      <c r="C126" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D126" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="C126" s="10"/>
+      <c r="D126" s="10"/>
       <c r="E126" s="10"/>
-      <c r="F126" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G126" s="11">
-        <v>33339</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+      <c r="F126" s="10"/>
+      <c r="G126" s="10"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="9" t="s">
         <v>149</v>
       </c>
       <c r="B127" s="9">
         <v>1333</v>
       </c>
-      <c r="C127" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D127" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="C127" s="10"/>
+      <c r="D127" s="10"/>
       <c r="E127" s="10"/>
-      <c r="F127" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G127" s="11">
-        <v>39414</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+      <c r="F127" s="10"/>
+      <c r="G127" s="10"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="9" t="s">
         <v>150</v>
       </c>
       <c r="B128" s="9">
         <v>1334</v>
       </c>
-      <c r="C128" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D128" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="C128" s="10"/>
+      <c r="D128" s="10"/>
       <c r="E128" s="10"/>
-      <c r="F128" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G128" s="11">
-        <v>37412</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
+      <c r="F128" s="10"/>
+      <c r="G128" s="10"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="9" t="s">
         <v>151</v>
       </c>
       <c r="B129" s="9">
         <v>1335</v>
       </c>
-      <c r="C129" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D129" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C129" s="10"/>
+      <c r="D129" s="10"/>
       <c r="E129" s="10"/>
-      <c r="F129" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G129" s="11">
-        <v>35435</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
+      <c r="F129" s="10"/>
+      <c r="G129" s="10"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
         <v>152</v>
       </c>
       <c r="B130" s="9">
         <v>1336</v>
       </c>
-      <c r="C130" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D130" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="C130" s="10"/>
+      <c r="D130" s="10"/>
       <c r="E130" s="10"/>
-      <c r="F130" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G130" s="11">
-        <v>33970</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
+      <c r="F130" s="10"/>
+      <c r="G130" s="10"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="9" t="s">
         <v>153</v>
       </c>
       <c r="B131" s="9">
         <v>1337</v>
       </c>
-      <c r="C131" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>266</v>
-      </c>
+      <c r="C131" s="10"/>
+      <c r="D131" s="10"/>
       <c r="E131" s="10"/>
-      <c r="F131" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G131" s="11">
-        <v>34545</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
+      <c r="F131" s="10"/>
+      <c r="G131" s="10"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="9" t="s">
         <v>154</v>
       </c>
       <c r="B132" s="9">
         <v>1338</v>
       </c>
-      <c r="C132" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="E132" s="11">
-        <f>VLOOKUP(B132,العقود!B$2:E$181,3,0)</f>
-        <v>46226</v>
-      </c>
-      <c r="F132" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G132" s="11">
-        <v>39840</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
+      <c r="C132" s="10"/>
+      <c r="D132" s="10"/>
+      <c r="E132" s="10"/>
+      <c r="F132" s="10"/>
+      <c r="G132" s="10"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="9" t="s">
         <v>155</v>
       </c>
       <c r="B133" s="9">
         <v>1340</v>
       </c>
-      <c r="C133" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D133" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="E133" s="11">
-        <f>VLOOKUP(B133,العقود!B$2:E$181,3,0)</f>
-        <v>46235</v>
-      </c>
-      <c r="F133" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G133" s="11">
-        <v>36901</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
+      <c r="C133" s="10"/>
+      <c r="D133" s="10"/>
+      <c r="E133" s="10"/>
+      <c r="F133" s="10"/>
+      <c r="G133" s="10"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="9" t="s">
         <v>156</v>
       </c>
       <c r="B134" s="9">
         <v>1341</v>
       </c>
-      <c r="C134" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D134" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="E134" s="11">
-        <f>VLOOKUP(B134,العقود!B$2:E$181,3,0)</f>
-        <v>46235</v>
-      </c>
-      <c r="F134" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="G134" s="11">
-        <v>37599</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
+      <c r="C134" s="10"/>
+      <c r="D134" s="10"/>
+      <c r="E134" s="10"/>
+      <c r="F134" s="10"/>
+      <c r="G134" s="10"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="9" t="s">
         <v>157</v>
       </c>
       <c r="B135" s="9">
         <v>1502</v>
       </c>
-      <c r="C135" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D135" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="E135" s="11">
-        <f>VLOOKUP(B135,العقود!B$2:E$181,3,0)</f>
-        <v>33831</v>
-      </c>
-      <c r="F135" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G135" s="11">
-        <v>20090</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
+      <c r="C135" s="10"/>
+      <c r="D135" s="10"/>
+      <c r="E135" s="10"/>
+      <c r="F135" s="10"/>
+      <c r="G135" s="10"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="9" t="s">
         <v>158</v>
       </c>
       <c r="B136" s="9">
         <v>1504</v>
       </c>
-      <c r="C136" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D136" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="E136" s="11">
-        <f>VLOOKUP(B136,العقود!B$2:E$181,3,0)</f>
-        <v>39672</v>
-      </c>
-      <c r="F136" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G136" s="11">
-        <v>27215</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
+      <c r="C136" s="10"/>
+      <c r="D136" s="10"/>
+      <c r="E136" s="10"/>
+      <c r="F136" s="10"/>
+      <c r="G136" s="10"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
         <v>159</v>
       </c>
       <c r="B137" s="9">
         <v>1505</v>
       </c>
-      <c r="C137" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D137" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="E137" s="11">
-        <f>VLOOKUP(B137,العقود!B$2:E$181,3,0)</f>
-        <v>42780</v>
-      </c>
-      <c r="F137" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G137" s="11">
-        <v>30157</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+      <c r="C137" s="10"/>
+      <c r="D137" s="10"/>
+      <c r="E137" s="10"/>
+      <c r="F137" s="10"/>
+      <c r="G137" s="10"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
         <v>160</v>
       </c>
       <c r="B138" s="9">
         <v>1506</v>
       </c>
-      <c r="C138" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D138" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E138" s="11">
-        <f>VLOOKUP(B138,العقود!B$2:E$181,3,0)</f>
-        <v>41782</v>
-      </c>
-      <c r="F138" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G138" s="11">
-        <v>32874</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
+      <c r="C138" s="10"/>
+      <c r="D138" s="10"/>
+      <c r="E138" s="10"/>
+      <c r="F138" s="10"/>
+      <c r="G138" s="10"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="9" t="s">
         <v>161</v>
       </c>
       <c r="B139" s="9">
         <v>1508</v>
       </c>
-      <c r="C139" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D139" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="E139" s="11">
-        <f>VLOOKUP(B139,العقود!B$2:E$181,3,0)</f>
-        <v>42072</v>
-      </c>
-      <c r="F139" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G139" s="11">
-        <v>33805</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
+      <c r="C139" s="10"/>
+      <c r="D139" s="10"/>
+      <c r="E139" s="10"/>
+      <c r="F139" s="10"/>
+      <c r="G139" s="10"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="9" t="s">
         <v>162</v>
       </c>
       <c r="B140" s="9">
         <v>1509</v>
       </c>
-      <c r="C140" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D140" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="E140" s="11">
-        <f>VLOOKUP(B140,العقود!B$2:E$181,3,0)</f>
-        <v>42387</v>
-      </c>
-      <c r="F140" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G140" s="11">
-        <v>32383</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
+      <c r="C140" s="10"/>
+      <c r="D140" s="10"/>
+      <c r="E140" s="10"/>
+      <c r="F140" s="10"/>
+      <c r="G140" s="10"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="9" t="s">
         <v>163</v>
       </c>
       <c r="B141" s="9">
         <v>1516</v>
       </c>
-      <c r="C141" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D141" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="E141" s="11">
-        <f>VLOOKUP(B141,العقود!B$2:E$181,3,0)</f>
-        <v>44005</v>
-      </c>
-      <c r="F141" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G141" s="11">
-        <v>34597</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
+      <c r="C141" s="10"/>
+      <c r="D141" s="10"/>
+      <c r="E141" s="10"/>
+      <c r="F141" s="10"/>
+      <c r="G141" s="10"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="9" t="s">
         <v>164</v>
       </c>
       <c r="B142" s="9">
         <v>1519</v>
       </c>
-      <c r="C142" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D142" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E142" s="11">
-        <f>VLOOKUP(B142,العقود!B$2:E$181,3,0)</f>
-        <v>44205</v>
-      </c>
-      <c r="F142" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G142" s="11">
-        <v>34117</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
+      <c r="C142" s="10"/>
+      <c r="D142" s="10"/>
+      <c r="E142" s="10"/>
+      <c r="F142" s="10"/>
+      <c r="G142" s="10"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="9" t="s">
         <v>165</v>
       </c>
       <c r="B143" s="9">
         <v>1520</v>
       </c>
-      <c r="C143" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D143" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="E143" s="11">
-        <f>VLOOKUP(B143,العقود!B$2:E$181,3,0)</f>
-        <v>44205</v>
-      </c>
-      <c r="F143" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G143" s="11">
-        <v>35650</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
+      <c r="C143" s="10"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="10"/>
+      <c r="F143" s="10"/>
+      <c r="G143" s="10"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="9" t="s">
         <v>166</v>
       </c>
       <c r="B144" s="9">
         <v>1523</v>
       </c>
-      <c r="C144" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D144" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E144" s="11">
-        <f>VLOOKUP(B144,العقود!B$2:E$181,3,0)</f>
-        <v>44321</v>
-      </c>
-      <c r="F144" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G144" s="11">
-        <v>28856</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
+      <c r="C144" s="10"/>
+      <c r="D144" s="10"/>
+      <c r="E144" s="10"/>
+      <c r="F144" s="10"/>
+      <c r="G144" s="10"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="9" t="s">
         <v>167</v>
       </c>
       <c r="B145" s="9">
         <v>1527</v>
       </c>
-      <c r="C145" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D145" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E145" s="11">
-        <f>VLOOKUP(B145,العقود!B$2:E$181,3,0)</f>
-        <v>44319</v>
-      </c>
-      <c r="F145" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="G145" s="11">
-        <v>29135</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
+      <c r="C145" s="10"/>
+      <c r="D145" s="10"/>
+      <c r="E145" s="10"/>
+      <c r="F145" s="10"/>
+      <c r="G145" s="10"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="9" t="s">
         <v>168</v>
       </c>
       <c r="B146" s="9">
         <v>1528</v>
       </c>
-      <c r="C146" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D146" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E146" s="11">
-        <f>VLOOKUP(B146,العقود!B$2:E$181,3,0)</f>
-        <v>44378</v>
-      </c>
-      <c r="F146" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G146" s="11">
-        <v>31190</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
+      <c r="C146" s="10"/>
+      <c r="D146" s="10"/>
+      <c r="E146" s="10"/>
+      <c r="F146" s="10"/>
+      <c r="G146" s="10"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="9" t="s">
         <v>169</v>
       </c>
       <c r="B147" s="9">
         <v>1530</v>
       </c>
-      <c r="C147" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D147" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E147" s="11">
-        <f>VLOOKUP(B147,العقود!B$2:E$181,3,0)</f>
-        <v>44524</v>
-      </c>
-      <c r="F147" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G147" s="11">
-        <v>36579</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
+      <c r="C147" s="10"/>
+      <c r="D147" s="10"/>
+      <c r="E147" s="10"/>
+      <c r="F147" s="10"/>
+      <c r="G147" s="10"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
         <v>170</v>
       </c>
       <c r="B148" s="9">
         <v>1531</v>
       </c>
-      <c r="C148" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D148" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E148" s="11">
-        <f>VLOOKUP(B148,العقود!B$2:E$181,3,0)</f>
-        <v>44529</v>
-      </c>
-      <c r="F148" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G148" s="11">
-        <v>34546</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
+      <c r="C148" s="10"/>
+      <c r="D148" s="10"/>
+      <c r="E148" s="10"/>
+      <c r="F148" s="10"/>
+      <c r="G148" s="10"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="9" t="s">
         <v>171</v>
       </c>
       <c r="B149" s="9">
         <v>1533</v>
       </c>
-      <c r="C149" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D149" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E149" s="11">
-        <f>VLOOKUP(B149,العقود!B$2:E$181,3,0)</f>
-        <v>44549</v>
-      </c>
-      <c r="F149" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G149" s="11">
-        <v>27395</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
+      <c r="C149" s="10"/>
+      <c r="D149" s="10"/>
+      <c r="E149" s="10"/>
+      <c r="F149" s="10"/>
+      <c r="G149" s="10"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
         <v>172</v>
       </c>
       <c r="B150" s="9">
         <v>1534</v>
       </c>
-      <c r="C150" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D150" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="E150" s="11">
-        <f>VLOOKUP(B150,العقود!B$2:E$181,3,0)</f>
-        <v>44579</v>
-      </c>
-      <c r="F150" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G150" s="11">
-        <v>34175</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
+      <c r="C150" s="10"/>
+      <c r="D150" s="10"/>
+      <c r="E150" s="10"/>
+      <c r="F150" s="10"/>
+      <c r="G150" s="10"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="9" t="s">
         <v>173</v>
       </c>
       <c r="B151" s="9">
         <v>1535</v>
       </c>
-      <c r="C151" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D151" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E151" s="11">
-        <f>VLOOKUP(B151,العقود!B$2:E$181,3,0)</f>
-        <v>44580</v>
-      </c>
-      <c r="F151" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G151" s="11">
-        <v>32270</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
+      <c r="C151" s="10"/>
+      <c r="D151" s="10"/>
+      <c r="E151" s="10"/>
+      <c r="F151" s="10"/>
+      <c r="G151" s="10"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="9" t="s">
         <v>174</v>
       </c>
       <c r="B152" s="9">
         <v>1536</v>
       </c>
-      <c r="C152" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D152" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E152" s="11">
-        <f>VLOOKUP(B152,العقود!B$2:E$181,3,0)</f>
-        <v>44580</v>
-      </c>
-      <c r="F152" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G152" s="11">
-        <v>35796</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
+      <c r="C152" s="10"/>
+      <c r="D152" s="10"/>
+      <c r="E152" s="10"/>
+      <c r="F152" s="10"/>
+      <c r="G152" s="10"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="9" t="s">
         <v>175</v>
       </c>
       <c r="B153" s="9">
         <v>1537</v>
       </c>
-      <c r="C153" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D153" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="E153" s="11">
-        <f>VLOOKUP(B153,العقود!B$2:E$181,3,0)</f>
-        <v>44562</v>
-      </c>
-      <c r="F153" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G153" s="11">
-        <v>31570</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
+      <c r="C153" s="10"/>
+      <c r="D153" s="10"/>
+      <c r="E153" s="10"/>
+      <c r="F153" s="10"/>
+      <c r="G153" s="10"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="9" t="s">
         <v>176</v>
       </c>
       <c r="B154" s="9">
         <v>1540</v>
       </c>
-      <c r="C154" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D154" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="E154" s="11">
-        <f>VLOOKUP(B154,العقود!B$2:E$181,3,0)</f>
-        <v>44587</v>
-      </c>
-      <c r="F154" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G154" s="11">
-        <v>36281</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
+      <c r="C154" s="10"/>
+      <c r="D154" s="10"/>
+      <c r="E154" s="10"/>
+      <c r="F154" s="10"/>
+      <c r="G154" s="10"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="9" t="s">
         <v>177</v>
       </c>
       <c r="B155" s="9">
         <v>1541</v>
       </c>
-      <c r="C155" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D155" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="E155" s="11">
-        <f>VLOOKUP(B155,العقود!B$2:E$181,3,0)</f>
-        <v>44606</v>
-      </c>
-      <c r="F155" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G155" s="11">
-        <v>29742</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
+      <c r="C155" s="10"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="10"/>
+      <c r="F155" s="10"/>
+      <c r="G155" s="10"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="9" t="s">
         <v>178</v>
       </c>
       <c r="B156" s="9">
         <v>1542</v>
       </c>
-      <c r="C156" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D156" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E156" s="11">
-        <f>VLOOKUP(B156,العقود!B$2:E$181,3,0)</f>
-        <v>44593</v>
-      </c>
-      <c r="F156" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G156" s="11">
-        <v>36378</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
+      <c r="C156" s="10"/>
+      <c r="D156" s="10"/>
+      <c r="E156" s="10"/>
+      <c r="F156" s="10"/>
+      <c r="G156" s="10"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="9" t="s">
         <v>179</v>
       </c>
       <c r="B157" s="9">
         <v>1544</v>
       </c>
-      <c r="C157" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D157" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E157" s="11">
-        <f>VLOOKUP(B157,العقود!B$2:E$181,3,0)</f>
-        <v>44606</v>
-      </c>
-      <c r="F157" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="G157" s="11">
-        <v>32509</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
+      <c r="C157" s="10"/>
+      <c r="D157" s="10"/>
+      <c r="E157" s="10"/>
+      <c r="F157" s="10"/>
+      <c r="G157" s="10"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="9" t="s">
         <v>180</v>
       </c>
       <c r="B158" s="9">
         <v>1545</v>
       </c>
-      <c r="C158" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D158" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E158" s="11">
-        <f>VLOOKUP(B158,العقود!B$2:E$181,3,0)</f>
-        <v>44628</v>
-      </c>
-      <c r="F158" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G158" s="11">
-        <v>33604</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
+      <c r="C158" s="10"/>
+      <c r="D158" s="10"/>
+      <c r="E158" s="10"/>
+      <c r="F158" s="10"/>
+      <c r="G158" s="10"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
         <v>181</v>
       </c>
       <c r="B159" s="9">
         <v>1551</v>
       </c>
-      <c r="C159" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D159" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E159" s="11">
-        <f>VLOOKUP(B159,العقود!B$2:E$181,3,0)</f>
-        <v>44657</v>
-      </c>
-      <c r="F159" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G159" s="11">
-        <v>36600</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
+      <c r="C159" s="10"/>
+      <c r="D159" s="10"/>
+      <c r="E159" s="10"/>
+      <c r="F159" s="10"/>
+      <c r="G159" s="10"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>182</v>
       </c>
       <c r="B160" s="9">
         <v>1552</v>
       </c>
-      <c r="C160" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D160" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E160" s="11">
-        <f>VLOOKUP(B160,العقود!B$2:E$181,3,0)</f>
-        <v>44657</v>
-      </c>
-      <c r="F160" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G160" s="11">
-        <v>35828</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
+      <c r="C160" s="10"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="10"/>
+      <c r="F160" s="10"/>
+      <c r="G160" s="10"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>183</v>
       </c>
       <c r="B161" s="9">
         <v>1553</v>
       </c>
-      <c r="C161" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D161" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E161" s="11">
-        <f>VLOOKUP(B161,العقود!B$2:E$181,3,0)</f>
-        <v>44657</v>
-      </c>
-      <c r="F161" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G161" s="11">
-        <v>33604</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
+      <c r="C161" s="10"/>
+      <c r="D161" s="10"/>
+      <c r="E161" s="10"/>
+      <c r="F161" s="10"/>
+      <c r="G161" s="10"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>184</v>
       </c>
       <c r="B162" s="9">
         <v>1554</v>
       </c>
-      <c r="C162" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D162" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="E162" s="11">
-        <f>VLOOKUP(B162,العقود!B$2:E$181,3,0)</f>
-        <v>44741</v>
-      </c>
-      <c r="F162" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="G162" s="11">
-        <v>29459</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
+      <c r="C162" s="10"/>
+      <c r="D162" s="10"/>
+      <c r="E162" s="10"/>
+      <c r="F162" s="10"/>
+      <c r="G162" s="10"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="9" t="s">
         <v>185</v>
       </c>
       <c r="B163" s="9">
         <v>1555</v>
       </c>
-      <c r="C163" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D163" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="E163" s="11">
-        <f>VLOOKUP(B163,العقود!B$2:E$181,3,0)</f>
-        <v>44774</v>
-      </c>
-      <c r="F163" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G163" s="11">
-        <v>32874</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
+      <c r="C163" s="10"/>
+      <c r="D163" s="10"/>
+      <c r="E163" s="10"/>
+      <c r="F163" s="10"/>
+      <c r="G163" s="10"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>186</v>
       </c>
       <c r="B164" s="9">
         <v>1557</v>
       </c>
-      <c r="C164" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D164" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E164" s="11">
-        <f>VLOOKUP(B164,العقود!B$2:E$181,3,0)</f>
-        <v>44801</v>
-      </c>
-      <c r="F164" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="G164" s="11">
-        <v>34420</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
+      <c r="C164" s="10"/>
+      <c r="D164" s="10"/>
+      <c r="E164" s="10"/>
+      <c r="F164" s="10"/>
+      <c r="G164" s="10"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>187</v>
       </c>
       <c r="B165" s="9">
         <v>1558</v>
       </c>
-      <c r="C165" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D165" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="E165" s="11">
-        <f>VLOOKUP(B165,العقود!B$2:E$181,3,0)</f>
-        <v>44804</v>
-      </c>
-      <c r="F165" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G165" s="11">
-        <v>33321</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
+      <c r="C165" s="10"/>
+      <c r="D165" s="10"/>
+      <c r="E165" s="10"/>
+      <c r="F165" s="10"/>
+      <c r="G165" s="10"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="9" t="s">
         <v>188</v>
       </c>
       <c r="B166" s="9">
         <v>1559</v>
       </c>
-      <c r="C166" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D166" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="E166" s="11">
-        <f>VLOOKUP(B166,العقود!B$2:E$181,3,0)</f>
-        <v>44804</v>
-      </c>
-      <c r="F166" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G166" s="11">
-        <v>33932</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
+      <c r="C166" s="10"/>
+      <c r="D166" s="10"/>
+      <c r="E166" s="10"/>
+      <c r="F166" s="10"/>
+      <c r="G166" s="10"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="9" t="s">
         <v>189</v>
       </c>
       <c r="B167" s="9">
         <v>1561</v>
       </c>
-      <c r="C167" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D167" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E167" s="11">
-        <f>VLOOKUP(B167,العقود!B$2:E$181,3,0)</f>
-        <v>44812</v>
-      </c>
-      <c r="F167" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G167" s="11">
-        <v>35288</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
+      <c r="C167" s="10"/>
+      <c r="D167" s="10"/>
+      <c r="E167" s="10"/>
+      <c r="F167" s="10"/>
+      <c r="G167" s="10"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="9" t="s">
         <v>190</v>
       </c>
       <c r="B168" s="9">
         <v>1562</v>
       </c>
-      <c r="C168" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D168" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="E168" s="11">
-        <f>VLOOKUP(B168,العقود!B$2:E$181,3,0)</f>
-        <v>44812</v>
-      </c>
-      <c r="F168" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G168" s="11">
-        <v>36518</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
+      <c r="C168" s="10"/>
+      <c r="D168" s="10"/>
+      <c r="E168" s="10"/>
+      <c r="F168" s="10"/>
+      <c r="G168" s="10"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="9" t="s">
         <v>191</v>
       </c>
       <c r="B169" s="9">
         <v>1563</v>
       </c>
-      <c r="C169" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D169" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="E169" s="11">
-        <f>VLOOKUP(B169,العقود!B$2:E$181,3,0)</f>
-        <v>44812</v>
-      </c>
-      <c r="F169" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="G169" s="11">
-        <v>36252</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
+      <c r="C169" s="10"/>
+      <c r="D169" s="10"/>
+      <c r="E169" s="10"/>
+      <c r="F169" s="10"/>
+      <c r="G169" s="10"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
         <v>192</v>
       </c>
       <c r="B170" s="9">
         <v>1565</v>
       </c>
-      <c r="C170" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D170" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E170" s="11">
-        <f>VLOOKUP(B170,العقود!B$2:E$181,3,0)</f>
-        <v>44875</v>
-      </c>
-      <c r="F170" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="G170" s="11">
-        <v>33018</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
+      <c r="C170" s="10"/>
+      <c r="D170" s="10"/>
+      <c r="E170" s="10"/>
+      <c r="F170" s="10"/>
+      <c r="G170" s="10"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="9" t="s">
         <v>193</v>
       </c>
       <c r="B171" s="9">
         <v>1566</v>
       </c>
-      <c r="C171" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D171" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E171" s="11">
-        <f>VLOOKUP(B171,العقود!B$2:E$181,3,0)</f>
-        <v>44877</v>
-      </c>
-      <c r="F171" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G171" s="11">
-        <v>36329</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
+      <c r="C171" s="10"/>
+      <c r="D171" s="10"/>
+      <c r="E171" s="10"/>
+      <c r="F171" s="10"/>
+      <c r="G171" s="10"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
         <v>194</v>
       </c>
       <c r="B172" s="9">
         <v>1567</v>
       </c>
-      <c r="C172" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D172" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="E172" s="11">
-        <f>VLOOKUP(B172,العقود!B$2:E$181,3,0)</f>
-        <v>44878</v>
-      </c>
-      <c r="F172" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="G172" s="11">
-        <v>34708</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
+      <c r="C172" s="10"/>
+      <c r="D172" s="10"/>
+      <c r="E172" s="10"/>
+      <c r="F172" s="10"/>
+      <c r="G172" s="10"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="9" t="s">
         <v>195</v>
       </c>
       <c r="B173" s="9">
         <v>1568</v>
       </c>
-      <c r="C173" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D173" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E173" s="11">
-        <f>VLOOKUP(B173,العقود!B$2:E$181,3,0)</f>
-        <v>44863</v>
-      </c>
-      <c r="F173" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="G173" s="11">
-        <v>31312</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
+      <c r="C173" s="10"/>
+      <c r="D173" s="10"/>
+      <c r="E173" s="10"/>
+      <c r="F173" s="10"/>
+      <c r="G173" s="10"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="9" t="s">
         <v>196</v>
       </c>
       <c r="B174" s="9">
         <v>1602</v>
       </c>
-      <c r="C174" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D174" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E174" s="11">
-        <f>VLOOKUP(B174,العقود!B$2:E$181,3,0)</f>
-        <v>45127</v>
-      </c>
-      <c r="F174" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="G174" s="11">
-        <v>36274</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
+      <c r="C174" s="10"/>
+      <c r="D174" s="10"/>
+      <c r="E174" s="10"/>
+      <c r="F174" s="10"/>
+      <c r="G174" s="10"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
         <v>197</v>
       </c>
       <c r="B175" s="9">
         <v>1606</v>
       </c>
-      <c r="C175" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D175" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E175" s="11">
-        <f>VLOOKUP(B175,العقود!B$2:E$181,3,0)</f>
-        <v>44081</v>
-      </c>
-      <c r="F175" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G175" s="11">
-        <v>27061</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
+      <c r="C175" s="10"/>
+      <c r="D175" s="10"/>
+      <c r="E175" s="10"/>
+      <c r="F175" s="10"/>
+      <c r="G175" s="10"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
         <v>198</v>
       </c>
       <c r="B176" s="9">
         <v>1608</v>
       </c>
-      <c r="C176" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D176" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="E176" s="11">
-        <f>VLOOKUP(B176,العقود!B$2:E$181,3,0)</f>
-        <v>45175</v>
-      </c>
-      <c r="F176" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G176" s="11">
-        <v>33445</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7">
+      <c r="C176" s="10"/>
+      <c r="D176" s="10"/>
+      <c r="E176" s="10"/>
+      <c r="F176" s="10"/>
+      <c r="G176" s="10"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
         <v>199</v>
       </c>
       <c r="B177" s="9">
         <v>1609</v>
       </c>
-      <c r="C177" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D177" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="E177" s="11">
-        <f>VLOOKUP(B177,العقود!B$2:E$181,3,0)</f>
-        <v>44604</v>
-      </c>
-      <c r="F177" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G177" s="11">
-        <v>29575</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7">
+      <c r="C177" s="10"/>
+      <c r="D177" s="10"/>
+      <c r="E177" s="10"/>
+      <c r="F177" s="10"/>
+      <c r="G177" s="10"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
         <v>200</v>
       </c>
       <c r="B178" s="9">
         <v>1611</v>
       </c>
-      <c r="C178" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D178" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E178" s="11">
-        <f>VLOOKUP(B178,العقود!B$2:E$181,3,0)</f>
-        <v>44713</v>
-      </c>
-      <c r="F178" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G178" s="11">
-        <v>35370</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
+      <c r="C178" s="10"/>
+      <c r="D178" s="10"/>
+      <c r="E178" s="10"/>
+      <c r="F178" s="10"/>
+      <c r="G178" s="10"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
         <v>201</v>
       </c>
       <c r="B179" s="9">
         <v>1612</v>
       </c>
-      <c r="C179" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D179" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E179" s="11">
-        <f>VLOOKUP(B179,العقود!B$2:E$181,3,0)</f>
-        <v>44713</v>
-      </c>
-      <c r="F179" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="G179" s="11">
-        <v>33165</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
+      <c r="C179" s="10"/>
+      <c r="D179" s="10"/>
+      <c r="E179" s="10"/>
+      <c r="F179" s="10"/>
+      <c r="G179" s="10"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
         <v>202</v>
       </c>
       <c r="B180" s="9">
         <v>1613</v>
       </c>
-      <c r="C180" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D180" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E180" s="11">
-        <f>VLOOKUP(B180,العقود!B$2:E$181,3,0)</f>
-        <v>44412</v>
-      </c>
-      <c r="F180" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G180" s="11">
-        <v>33469</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7">
+      <c r="C180" s="10"/>
+      <c r="D180" s="10"/>
+      <c r="E180" s="10"/>
+      <c r="F180" s="10"/>
+      <c r="G180" s="10"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
         <v>203</v>
       </c>
       <c r="B181" s="9">
         <v>1614</v>
       </c>
-      <c r="C181" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D181" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E181" s="11">
-        <f>VLOOKUP(B181,العقود!B$2:E$181,3,0)</f>
-        <v>44412</v>
-      </c>
-      <c r="F181" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G181" s="11">
-        <v>33999</v>
-      </c>
+      <c r="C181" s="10"/>
+      <c r="D181" s="10"/>
+      <c r="E181" s="10"/>
+      <c r="F181" s="10"/>
+      <c r="G181" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
